--- a/controllers/relatorios/base/RELATORIO INSPECAO.xlsx
+++ b/controllers/relatorios/base/RELATORIO INSPECAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrone\SynologyDrive\fortanks_novo\controllers\relatorios\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817B0253-59A5-4576-9505-E7E9A01ADA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E56AB1-5B56-4B30-9971-1CD7B62B6258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="1" sheetId="203" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1'!$A$5:$AO$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$AO$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1'!$C$7:$AQ$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$B$2:$AR$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
     <author>fortes</author>
   </authors>
   <commentList>
-    <comment ref="AI1" authorId="0" shapeId="0" xr:uid="{BAC16819-41E8-43C2-90C1-7544878A684D}">
+    <comment ref="AK3" authorId="0" shapeId="0" xr:uid="{BAC16819-41E8-43C2-90C1-7544878A684D}">
       <text>
         <r>
           <rPr>
@@ -1832,6 +1832,12 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2198,12 +2204,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2229,15 +2229,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>134409</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>25135</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>1840</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>170683</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2279,15 +2279,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>123056</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>157617</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>29047</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>29049</xdr:colOff>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>250282</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2322,10 +2322,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2628,746 +2624,681 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:BQ76"/>
+  <dimension ref="C2:BS79"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="7" width="2.53515625" customWidth="1"/>
-    <col min="8" max="8" width="3.15234375" customWidth="1"/>
-    <col min="9" max="24" width="2.53515625" customWidth="1"/>
-    <col min="25" max="25" width="2.84375" customWidth="1"/>
-    <col min="26" max="28" width="2.53515625" customWidth="1"/>
-    <col min="29" max="29" width="2.84375" customWidth="1"/>
-    <col min="30" max="41" width="2.53515625" customWidth="1"/>
-    <col min="42" max="42" width="1.3828125" customWidth="1"/>
-    <col min="44" max="44" width="2.07421875" customWidth="1"/>
-    <col min="45" max="45" width="2.4609375" customWidth="1"/>
-    <col min="46" max="46" width="1.69140625" customWidth="1"/>
-    <col min="47" max="47" width="2.61328125" customWidth="1"/>
-    <col min="48" max="48" width="3" customWidth="1"/>
-    <col min="49" max="49" width="2.3828125" customWidth="1"/>
-    <col min="50" max="50" width="2.4609375" customWidth="1"/>
-    <col min="51" max="51" width="3" customWidth="1"/>
+    <col min="1" max="1" width="16.3046875" customWidth="1"/>
+    <col min="2" max="2" width="2.15234375" customWidth="1"/>
+    <col min="3" max="3" width="2" customWidth="1"/>
+    <col min="4" max="9" width="2.53515625" customWidth="1"/>
+    <col min="10" max="10" width="3.15234375" customWidth="1"/>
+    <col min="11" max="26" width="2.53515625" customWidth="1"/>
+    <col min="27" max="27" width="2.84375" customWidth="1"/>
+    <col min="28" max="30" width="2.53515625" customWidth="1"/>
+    <col min="31" max="31" width="2.84375" customWidth="1"/>
+    <col min="32" max="43" width="2.53515625" customWidth="1"/>
+    <col min="44" max="44" width="1.3828125" customWidth="1"/>
+    <col min="46" max="46" width="2.07421875" customWidth="1"/>
+    <col min="47" max="47" width="2.4609375" customWidth="1"/>
+    <col min="48" max="48" width="1.69140625" customWidth="1"/>
+    <col min="49" max="49" width="2.61328125" customWidth="1"/>
+    <col min="50" max="50" width="3" customWidth="1"/>
+    <col min="51" max="51" width="2.3828125" customWidth="1"/>
+    <col min="52" max="52" width="2.4609375" customWidth="1"/>
+    <col min="53" max="53" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="221"/>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="227" t="s">
+    <row r="2" spans="3:43" ht="10.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C3" s="223"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="224"/>
+      <c r="H3" s="224"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="224"/>
+      <c r="L3" s="225"/>
+      <c r="M3" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="228"/>
-      <c r="M1" s="228"/>
-      <c r="N1" s="228"/>
-      <c r="O1" s="228"/>
-      <c r="P1" s="228"/>
-      <c r="Q1" s="228"/>
-      <c r="R1" s="228"/>
-      <c r="S1" s="228"/>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
-      <c r="W1" s="228"/>
-      <c r="X1" s="228"/>
-      <c r="Y1" s="228"/>
-      <c r="Z1" s="228"/>
-      <c r="AA1" s="228"/>
-      <c r="AB1" s="229"/>
-      <c r="AC1" s="230" t="s">
+      <c r="N3" s="230"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="230"/>
+      <c r="Q3" s="230"/>
+      <c r="R3" s="230"/>
+      <c r="S3" s="230"/>
+      <c r="T3" s="230"/>
+      <c r="U3" s="230"/>
+      <c r="V3" s="230"/>
+      <c r="W3" s="230"/>
+      <c r="X3" s="230"/>
+      <c r="Y3" s="230"/>
+      <c r="Z3" s="230"/>
+      <c r="AA3" s="230"/>
+      <c r="AB3" s="230"/>
+      <c r="AC3" s="230"/>
+      <c r="AD3" s="231"/>
+      <c r="AE3" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="AD1" s="231"/>
-      <c r="AE1" s="231"/>
-      <c r="AF1" s="231"/>
-      <c r="AG1" s="231" t="s">
+      <c r="AF3" s="233"/>
+      <c r="AG3" s="233"/>
+      <c r="AH3" s="233"/>
+      <c r="AI3" s="233" t="s">
         <v>46</v>
       </c>
-      <c r="AH1" s="231"/>
-      <c r="AI1" s="75"/>
-      <c r="AJ1" s="241" t="s">
+      <c r="AJ3" s="233"/>
+      <c r="AK3" s="75"/>
+      <c r="AL3" s="243" t="s">
         <v>79</v>
       </c>
-      <c r="AK1" s="241"/>
-      <c r="AL1" s="241"/>
-      <c r="AM1" s="241"/>
-      <c r="AN1" s="241"/>
-      <c r="AO1" s="242"/>
-    </row>
-    <row r="2" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="149"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="232" t="s">
+      <c r="AM3" s="243"/>
+      <c r="AN3" s="243"/>
+      <c r="AO3" s="243"/>
+      <c r="AP3" s="243"/>
+      <c r="AQ3" s="244"/>
+    </row>
+    <row r="4" spans="3:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="151"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="234" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="234" t="s">
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="236" t="s">
         <v>80</v>
       </c>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="234"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234"/>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="234"/>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="236" t="s">
+      <c r="R4" s="236"/>
+      <c r="S4" s="236"/>
+      <c r="T4" s="236"/>
+      <c r="U4" s="236"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="236"/>
+      <c r="X4" s="236"/>
+      <c r="Y4" s="236"/>
+      <c r="Z4" s="236"/>
+      <c r="AA4" s="236"/>
+      <c r="AB4" s="236"/>
+      <c r="AC4" s="236"/>
+      <c r="AD4" s="237"/>
+      <c r="AE4" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238" t="s">
+      <c r="AF4" s="239"/>
+      <c r="AG4" s="239"/>
+      <c r="AH4" s="240" t="s">
         <v>72</v>
       </c>
-      <c r="AG2" s="238"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="238"/>
-      <c r="AJ2" s="238"/>
-      <c r="AK2" s="238"/>
-      <c r="AL2" s="238"/>
-      <c r="AM2" s="238"/>
-      <c r="AN2" s="238"/>
-      <c r="AO2" s="239"/>
-    </row>
-    <row r="3" spans="1:41" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="224"/>
-      <c r="B3" s="225"/>
-      <c r="C3" s="225"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="225"/>
-      <c r="F3" s="225"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="225"/>
-      <c r="I3" s="225"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="197" t="s">
+      <c r="AI4" s="240"/>
+      <c r="AJ4" s="240"/>
+      <c r="AK4" s="240"/>
+      <c r="AL4" s="240"/>
+      <c r="AM4" s="240"/>
+      <c r="AN4" s="240"/>
+      <c r="AO4" s="240"/>
+      <c r="AP4" s="240"/>
+      <c r="AQ4" s="241"/>
+    </row>
+    <row r="5" spans="3:43" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C5" s="226"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="228"/>
+      <c r="M5" s="199" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="199" t="s">
+      <c r="N5" s="200"/>
+      <c r="O5" s="200"/>
+      <c r="P5" s="200"/>
+      <c r="Q5" s="201" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="199"/>
-      <c r="Q3" s="199"/>
-      <c r="R3" s="199"/>
-      <c r="S3" s="199"/>
-      <c r="T3" s="199"/>
-      <c r="U3" s="199"/>
-      <c r="V3" s="199"/>
-      <c r="W3" s="199"/>
-      <c r="X3" s="199"/>
-      <c r="Y3" s="199"/>
-      <c r="Z3" s="199"/>
-      <c r="AA3" s="199"/>
-      <c r="AB3" s="199"/>
-      <c r="AC3" s="199"/>
-      <c r="AD3" s="199"/>
-      <c r="AE3" s="199"/>
-      <c r="AF3" s="199"/>
-      <c r="AG3" s="199"/>
-      <c r="AH3" s="199"/>
-      <c r="AI3" s="199"/>
-      <c r="AJ3" s="199"/>
-      <c r="AK3" s="199"/>
-      <c r="AL3" s="199"/>
-      <c r="AM3" s="199"/>
-      <c r="AN3" s="199"/>
-      <c r="AO3" s="200"/>
-    </row>
-    <row r="4" spans="1:41" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="201" t="s">
+      <c r="R5" s="201"/>
+      <c r="S5" s="201"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="201"/>
+      <c r="V5" s="201"/>
+      <c r="W5" s="201"/>
+      <c r="X5" s="201"/>
+      <c r="Y5" s="201"/>
+      <c r="Z5" s="201"/>
+      <c r="AA5" s="201"/>
+      <c r="AB5" s="201"/>
+      <c r="AC5" s="201"/>
+      <c r="AD5" s="201"/>
+      <c r="AE5" s="201"/>
+      <c r="AF5" s="201"/>
+      <c r="AG5" s="201"/>
+      <c r="AH5" s="201"/>
+      <c r="AI5" s="201"/>
+      <c r="AJ5" s="201"/>
+      <c r="AK5" s="201"/>
+      <c r="AL5" s="201"/>
+      <c r="AM5" s="201"/>
+      <c r="AN5" s="201"/>
+      <c r="AO5" s="201"/>
+      <c r="AP5" s="201"/>
+      <c r="AQ5" s="202"/>
+    </row>
+    <row r="6" spans="3:43" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="3:43" ht="16" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="204" t="s">
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="204"/>
+      <c r="H7" s="204"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="205"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="205"/>
-      <c r="N5" s="205"/>
-      <c r="O5" s="205"/>
-      <c r="P5" s="205"/>
-      <c r="Q5" s="205"/>
-      <c r="R5" s="205"/>
-      <c r="S5" s="205"/>
-      <c r="T5" s="205"/>
-      <c r="U5" s="205"/>
-      <c r="V5" s="205"/>
-      <c r="W5" s="205"/>
-      <c r="X5" s="205"/>
-      <c r="Y5" s="205"/>
-      <c r="Z5" s="205"/>
-      <c r="AA5" s="205"/>
-      <c r="AB5" s="206"/>
-      <c r="AC5" s="207" t="s">
+      <c r="K7" s="207"/>
+      <c r="L7" s="207"/>
+      <c r="M7" s="207"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
+      <c r="P7" s="207"/>
+      <c r="Q7" s="207"/>
+      <c r="R7" s="207"/>
+      <c r="S7" s="207"/>
+      <c r="T7" s="207"/>
+      <c r="U7" s="207"/>
+      <c r="V7" s="207"/>
+      <c r="W7" s="207"/>
+      <c r="X7" s="207"/>
+      <c r="Y7" s="207"/>
+      <c r="Z7" s="207"/>
+      <c r="AA7" s="207"/>
+      <c r="AB7" s="207"/>
+      <c r="AC7" s="207"/>
+      <c r="AD7" s="208"/>
+      <c r="AE7" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="AD5" s="208"/>
-      <c r="AE5" s="208"/>
-      <c r="AF5" s="208"/>
-      <c r="AG5" s="208"/>
-      <c r="AH5" s="208"/>
-      <c r="AI5" s="208"/>
-      <c r="AJ5" s="208"/>
-      <c r="AK5" s="208"/>
-      <c r="AL5" s="208"/>
-      <c r="AM5" s="208"/>
-      <c r="AN5" s="208"/>
-      <c r="AO5" s="209"/>
-    </row>
-    <row r="6" spans="1:41" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="210" t="s">
+      <c r="AF7" s="210"/>
+      <c r="AG7" s="210"/>
+      <c r="AH7" s="210"/>
+      <c r="AI7" s="210"/>
+      <c r="AJ7" s="210"/>
+      <c r="AK7" s="210"/>
+      <c r="AL7" s="210"/>
+      <c r="AM7" s="210"/>
+      <c r="AN7" s="210"/>
+      <c r="AO7" s="210"/>
+      <c r="AP7" s="210"/>
+      <c r="AQ7" s="211"/>
+    </row>
+    <row r="8" spans="3:43" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C8" s="212" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="211"/>
-      <c r="C6" s="211"/>
-      <c r="D6" s="211"/>
-      <c r="E6" s="211"/>
-      <c r="F6" s="211"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="213" t="s">
+      <c r="D8" s="213"/>
+      <c r="E8" s="213"/>
+      <c r="F8" s="213"/>
+      <c r="G8" s="213"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="214"/>
+      <c r="J8" s="215" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="214"/>
-      <c r="J6" s="214"/>
-      <c r="K6" s="214"/>
-      <c r="L6" s="214"/>
-      <c r="M6" s="214"/>
-      <c r="N6" s="214"/>
-      <c r="O6" s="214"/>
-      <c r="P6" s="214"/>
-      <c r="Q6" s="214"/>
-      <c r="R6" s="214"/>
-      <c r="S6" s="214"/>
-      <c r="T6" s="214"/>
-      <c r="U6" s="214"/>
-      <c r="V6" s="214"/>
-      <c r="W6" s="214"/>
-      <c r="X6" s="214"/>
-      <c r="Y6" s="214"/>
-      <c r="Z6" s="214"/>
-      <c r="AA6" s="214"/>
-      <c r="AB6" s="215"/>
-      <c r="AC6" s="216" t="s">
+      <c r="K8" s="216"/>
+      <c r="L8" s="216"/>
+      <c r="M8" s="216"/>
+      <c r="N8" s="216"/>
+      <c r="O8" s="216"/>
+      <c r="P8" s="216"/>
+      <c r="Q8" s="216"/>
+      <c r="R8" s="216"/>
+      <c r="S8" s="216"/>
+      <c r="T8" s="216"/>
+      <c r="U8" s="216"/>
+      <c r="V8" s="216"/>
+      <c r="W8" s="216"/>
+      <c r="X8" s="216"/>
+      <c r="Y8" s="216"/>
+      <c r="Z8" s="216"/>
+      <c r="AA8" s="216"/>
+      <c r="AB8" s="216"/>
+      <c r="AC8" s="216"/>
+      <c r="AD8" s="217"/>
+      <c r="AE8" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="AD6" s="217"/>
-      <c r="AE6" s="217"/>
-      <c r="AF6" s="218" t="s">
+      <c r="AF8" s="219"/>
+      <c r="AG8" s="219"/>
+      <c r="AH8" s="220" t="s">
         <v>84</v>
       </c>
-      <c r="AG6" s="218"/>
-      <c r="AH6" s="219"/>
-      <c r="AI6" s="220" t="s">
+      <c r="AI8" s="220"/>
+      <c r="AJ8" s="221"/>
+      <c r="AK8" s="222" t="s">
         <v>8</v>
       </c>
-      <c r="AJ6" s="218"/>
-      <c r="AK6" s="218"/>
-      <c r="AL6" s="218" t="s">
+      <c r="AL8" s="220"/>
+      <c r="AM8" s="220"/>
+      <c r="AN8" s="220" t="s">
         <v>85</v>
       </c>
-      <c r="AM6" s="218"/>
-      <c r="AN6" s="218"/>
-      <c r="AO6" s="240"/>
-    </row>
-    <row r="7" spans="1:41" ht="5.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="8" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="190" t="s">
+      <c r="AO8" s="220"/>
+      <c r="AP8" s="220"/>
+      <c r="AQ8" s="242"/>
+    </row>
+    <row r="9" spans="3:43" ht="5.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="10" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="191"/>
-      <c r="C8" s="191"/>
-      <c r="D8" s="191"/>
-      <c r="E8" s="191"/>
-      <c r="F8" s="192" t="s">
+      <c r="D10" s="193"/>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193"/>
+      <c r="G10" s="193"/>
+      <c r="H10" s="194" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="193"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="192" t="s">
+      <c r="I10" s="195"/>
+      <c r="J10" s="196"/>
+      <c r="K10" s="194" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="193"/>
-      <c r="K8" s="194"/>
-      <c r="L8" s="188" t="s">
+      <c r="L10" s="195"/>
+      <c r="M10" s="196"/>
+      <c r="N10" s="190" t="s">
         <v>88</v>
       </c>
-      <c r="M8" s="188"/>
-      <c r="N8" s="188"/>
-      <c r="O8" s="188" t="s">
+      <c r="O10" s="190"/>
+      <c r="P10" s="190"/>
+      <c r="Q10" s="190" t="s">
         <v>89</v>
       </c>
-      <c r="P8" s="188"/>
-      <c r="Q8" s="188"/>
-      <c r="R8" s="188" t="s">
+      <c r="R10" s="190"/>
+      <c r="S10" s="190"/>
+      <c r="T10" s="190" t="s">
         <v>90</v>
       </c>
-      <c r="S8" s="188"/>
-      <c r="T8" s="188"/>
-      <c r="U8" s="188" t="s">
+      <c r="U10" s="190"/>
+      <c r="V10" s="190"/>
+      <c r="W10" s="190" t="s">
         <v>91</v>
       </c>
-      <c r="V8" s="188"/>
-      <c r="W8" s="188"/>
-      <c r="X8" s="188" t="s">
+      <c r="X10" s="190"/>
+      <c r="Y10" s="190"/>
+      <c r="Z10" s="190" t="s">
         <v>96</v>
       </c>
-      <c r="Y8" s="188"/>
-      <c r="Z8" s="188"/>
-      <c r="AA8" s="188" t="s">
+      <c r="AA10" s="190"/>
+      <c r="AB10" s="190"/>
+      <c r="AC10" s="190" t="s">
         <v>92</v>
       </c>
-      <c r="AB8" s="188"/>
-      <c r="AC8" s="188"/>
-      <c r="AD8" s="188" t="s">
+      <c r="AD10" s="190"/>
+      <c r="AE10" s="190"/>
+      <c r="AF10" s="190" t="s">
         <v>93</v>
       </c>
-      <c r="AE8" s="188"/>
-      <c r="AF8" s="188"/>
-      <c r="AG8" s="188" t="s">
+      <c r="AG10" s="190"/>
+      <c r="AH10" s="190"/>
+      <c r="AI10" s="190" t="s">
         <v>94</v>
       </c>
-      <c r="AH8" s="188"/>
-      <c r="AI8" s="188"/>
-      <c r="AJ8" s="188" t="s">
+      <c r="AJ10" s="190"/>
+      <c r="AK10" s="190"/>
+      <c r="AL10" s="190" t="s">
         <v>95</v>
       </c>
-      <c r="AK8" s="188"/>
-      <c r="AL8" s="188"/>
-      <c r="AM8" s="188" t="s">
+      <c r="AM10" s="190"/>
+      <c r="AN10" s="190"/>
+      <c r="AO10" s="190" t="s">
         <v>97</v>
       </c>
-      <c r="AN8" s="188"/>
-      <c r="AO8" s="189"/>
-    </row>
-    <row r="9" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="195" t="s">
+      <c r="AP10" s="190"/>
+      <c r="AQ10" s="191"/>
+    </row>
+    <row r="11" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="197" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="196"/>
-      <c r="E9" s="196"/>
-      <c r="F9" s="183" t="s">
+      <c r="D11" s="198"/>
+      <c r="E11" s="198"/>
+      <c r="F11" s="198"/>
+      <c r="G11" s="198"/>
+      <c r="H11" s="185" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183" t="s">
+      <c r="I11" s="185"/>
+      <c r="J11" s="185"/>
+      <c r="K11" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="183"/>
-      <c r="K9" s="183"/>
-      <c r="L9" s="183" t="s">
+      <c r="L11" s="185"/>
+      <c r="M11" s="185"/>
+      <c r="N11" s="185" t="s">
         <v>100</v>
       </c>
-      <c r="M9" s="183"/>
-      <c r="N9" s="183"/>
-      <c r="O9" s="183" t="s">
+      <c r="O11" s="185"/>
+      <c r="P11" s="185"/>
+      <c r="Q11" s="185" t="s">
         <v>101</v>
       </c>
-      <c r="P9" s="183"/>
-      <c r="Q9" s="183"/>
-      <c r="R9" s="183" t="s">
+      <c r="R11" s="185"/>
+      <c r="S11" s="185"/>
+      <c r="T11" s="185" t="s">
         <v>102</v>
       </c>
-      <c r="S9" s="183"/>
-      <c r="T9" s="183"/>
-      <c r="U9" s="183" t="s">
+      <c r="U11" s="185"/>
+      <c r="V11" s="185"/>
+      <c r="W11" s="185" t="s">
         <v>103</v>
       </c>
-      <c r="V9" s="183"/>
-      <c r="W9" s="183"/>
-      <c r="X9" s="183" t="s">
+      <c r="X11" s="185"/>
+      <c r="Y11" s="185"/>
+      <c r="Z11" s="185" t="s">
         <v>104</v>
       </c>
-      <c r="Y9" s="183"/>
-      <c r="Z9" s="183"/>
-      <c r="AA9" s="183" t="s">
+      <c r="AA11" s="185"/>
+      <c r="AB11" s="185"/>
+      <c r="AC11" s="185" t="s">
         <v>105</v>
       </c>
-      <c r="AB9" s="183"/>
-      <c r="AC9" s="183"/>
-      <c r="AD9" s="183" t="s">
+      <c r="AD11" s="185"/>
+      <c r="AE11" s="185"/>
+      <c r="AF11" s="185" t="s">
         <v>106</v>
       </c>
-      <c r="AE9" s="183"/>
-      <c r="AF9" s="183"/>
-      <c r="AG9" s="183" t="s">
+      <c r="AG11" s="185"/>
+      <c r="AH11" s="185"/>
+      <c r="AI11" s="185" t="s">
         <v>107</v>
       </c>
-      <c r="AH9" s="183"/>
-      <c r="AI9" s="183"/>
-      <c r="AJ9" s="183" t="s">
+      <c r="AJ11" s="185"/>
+      <c r="AK11" s="185"/>
+      <c r="AL11" s="185" t="s">
         <v>108</v>
       </c>
-      <c r="AK9" s="183"/>
-      <c r="AL9" s="183"/>
-      <c r="AM9" s="183" t="s">
+      <c r="AM11" s="185"/>
+      <c r="AN11" s="185"/>
+      <c r="AO11" s="185" t="s">
         <v>109</v>
       </c>
-      <c r="AN9" s="183"/>
-      <c r="AO9" s="184"/>
-    </row>
-    <row r="10" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="185" t="s">
+      <c r="AP11" s="185"/>
+      <c r="AQ11" s="186"/>
+    </row>
+    <row r="12" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C12" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="186"/>
-      <c r="C10" s="186"/>
-      <c r="D10" s="186"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="183" t="s">
+      <c r="D12" s="188"/>
+      <c r="E12" s="188"/>
+      <c r="F12" s="188"/>
+      <c r="G12" s="189"/>
+      <c r="H12" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183" t="s">
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="185" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="183"/>
-      <c r="K10" s="183"/>
-      <c r="L10" s="183" t="s">
+      <c r="L12" s="185"/>
+      <c r="M12" s="185"/>
+      <c r="N12" s="185" t="s">
         <v>112</v>
       </c>
-      <c r="M10" s="183"/>
-      <c r="N10" s="183"/>
-      <c r="O10" s="183" t="s">
+      <c r="O12" s="185"/>
+      <c r="P12" s="185"/>
+      <c r="Q12" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="183"/>
-      <c r="R10" s="183" t="s">
+      <c r="R12" s="185"/>
+      <c r="S12" s="185"/>
+      <c r="T12" s="185" t="s">
         <v>114</v>
       </c>
-      <c r="S10" s="183"/>
-      <c r="T10" s="183"/>
-      <c r="U10" s="183" t="s">
+      <c r="U12" s="185"/>
+      <c r="V12" s="185"/>
+      <c r="W12" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="V10" s="183"/>
-      <c r="W10" s="183"/>
-      <c r="X10" s="183" t="s">
+      <c r="X12" s="185"/>
+      <c r="Y12" s="185"/>
+      <c r="Z12" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="Y10" s="183"/>
-      <c r="Z10" s="183"/>
-      <c r="AA10" s="183" t="s">
+      <c r="AA12" s="185"/>
+      <c r="AB12" s="185"/>
+      <c r="AC12" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="AB10" s="183"/>
-      <c r="AC10" s="183"/>
-      <c r="AD10" s="183" t="s">
+      <c r="AD12" s="185"/>
+      <c r="AE12" s="185"/>
+      <c r="AF12" s="185" t="s">
         <v>118</v>
       </c>
-      <c r="AE10" s="183"/>
-      <c r="AF10" s="183"/>
-      <c r="AG10" s="183" t="s">
+      <c r="AG12" s="185"/>
+      <c r="AH12" s="185"/>
+      <c r="AI12" s="185" t="s">
         <v>119</v>
       </c>
-      <c r="AH10" s="183"/>
-      <c r="AI10" s="183"/>
-      <c r="AJ10" s="183" t="s">
+      <c r="AJ12" s="185"/>
+      <c r="AK12" s="185"/>
+      <c r="AL12" s="185" t="s">
         <v>120</v>
       </c>
-      <c r="AK10" s="183"/>
-      <c r="AL10" s="183"/>
-      <c r="AM10" s="183" t="s">
+      <c r="AM12" s="185"/>
+      <c r="AN12" s="185"/>
+      <c r="AO12" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="AN10" s="183"/>
-      <c r="AO10" s="184"/>
-    </row>
-    <row r="11" spans="1:41" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="179" t="s">
+      <c r="AP12" s="185"/>
+      <c r="AQ12" s="186"/>
+    </row>
+    <row r="13" spans="3:43" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C13" s="181" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="180"/>
-      <c r="C11" s="180"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="181" t="s">
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="183" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="181" t="s">
+      <c r="I13" s="183"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="183" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="181"/>
-      <c r="K11" s="181"/>
-      <c r="L11" s="181" t="s">
+      <c r="L13" s="183"/>
+      <c r="M13" s="183"/>
+      <c r="N13" s="183" t="s">
         <v>124</v>
       </c>
-      <c r="M11" s="181"/>
-      <c r="N11" s="181"/>
-      <c r="O11" s="181" t="s">
+      <c r="O13" s="183"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="183" t="s">
         <v>125</v>
       </c>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="181"/>
-      <c r="R11" s="181" t="s">
+      <c r="R13" s="183"/>
+      <c r="S13" s="183"/>
+      <c r="T13" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="S11" s="181"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181" t="s">
+      <c r="U13" s="183"/>
+      <c r="V13" s="183"/>
+      <c r="W13" s="183" t="s">
         <v>127</v>
       </c>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181" t="s">
+      <c r="X13" s="183"/>
+      <c r="Y13" s="183"/>
+      <c r="Z13" s="183" t="s">
         <v>128</v>
       </c>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181" t="s">
+      <c r="AA13" s="183"/>
+      <c r="AB13" s="183"/>
+      <c r="AC13" s="183" t="s">
         <v>129</v>
       </c>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181" t="s">
+      <c r="AD13" s="183"/>
+      <c r="AE13" s="183"/>
+      <c r="AF13" s="183" t="s">
         <v>130</v>
       </c>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="181" t="s">
+      <c r="AG13" s="183"/>
+      <c r="AH13" s="183"/>
+      <c r="AI13" s="183" t="s">
         <v>131</v>
       </c>
-      <c r="AH11" s="181"/>
-      <c r="AI11" s="181"/>
-      <c r="AJ11" s="181" t="s">
+      <c r="AJ13" s="183"/>
+      <c r="AK13" s="183"/>
+      <c r="AL13" s="183" t="s">
         <v>132</v>
       </c>
-      <c r="AK11" s="181"/>
-      <c r="AL11" s="181"/>
-      <c r="AM11" s="181" t="s">
+      <c r="AM13" s="183"/>
+      <c r="AN13" s="183"/>
+      <c r="AO13" s="183" t="s">
         <v>133</v>
       </c>
-      <c r="AN11" s="181"/>
-      <c r="AO11" s="181"/>
-    </row>
-    <row r="12" spans="1:41" ht="3" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:41" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="14" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="76" t="s">
+      <c r="AP13" s="183"/>
+      <c r="AQ13" s="183"/>
+    </row>
+    <row r="14" spans="3:43" ht="3" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="3:43" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="16" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C16" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="77"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="77"/>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="77"/>
-      <c r="AA14" s="77"/>
-      <c r="AB14" s="77"/>
-      <c r="AC14" s="78"/>
-      <c r="AD14" s="79" t="s">
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="77"/>
+      <c r="T16" s="77"/>
+      <c r="U16" s="77"/>
+      <c r="V16" s="77"/>
+      <c r="W16" s="77"/>
+      <c r="X16" s="77"/>
+      <c r="Y16" s="77"/>
+      <c r="Z16" s="77"/>
+      <c r="AA16" s="77"/>
+      <c r="AB16" s="77"/>
+      <c r="AC16" s="77"/>
+      <c r="AD16" s="77"/>
+      <c r="AE16" s="78"/>
+      <c r="AF16" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AE14" s="80"/>
-      <c r="AF14" s="80"/>
-      <c r="AG14" s="80"/>
-      <c r="AH14" s="80"/>
-      <c r="AI14" s="80"/>
-      <c r="AJ14" s="80"/>
-      <c r="AK14" s="80"/>
-      <c r="AL14" s="80"/>
-      <c r="AM14" s="80"/>
-      <c r="AN14" s="80"/>
-      <c r="AO14" s="81"/>
-    </row>
-    <row r="15" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16"/>
-      <c r="B15" s="74" t="s">
+      <c r="AG16" s="80"/>
+      <c r="AH16" s="80"/>
+      <c r="AI16" s="80"/>
+      <c r="AJ16" s="80"/>
+      <c r="AK16" s="80"/>
+      <c r="AL16" s="80"/>
+      <c r="AM16" s="80"/>
+      <c r="AN16" s="80"/>
+      <c r="AO16" s="80"/>
+      <c r="AP16" s="80"/>
+      <c r="AQ16" s="81"/>
+    </row>
+    <row r="17" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C17" s="16"/>
+      <c r="D17" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="2"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="43" t="s">
+      <c r="E17" s="6"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="3"/>
+      <c r="AH17" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG15" s="39" t="s">
+      <c r="AI17" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="42"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="39" t="s">
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="41"/>
+      <c r="AL17" s="42"/>
+      <c r="AM17" s="43"/>
+      <c r="AN17" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM15" s="40"/>
-      <c r="AN15" s="14"/>
-      <c r="AO15" s="17"/>
-    </row>
-    <row r="16" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="10" t="s">
+      <c r="AO17" s="40"/>
+      <c r="AP17" s="14"/>
+      <c r="AQ17" s="17"/>
+    </row>
+    <row r="18" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C18" s="18"/>
+      <c r="D18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="107" t="s">
+      <c r="E18" s="10"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="AE18" s="11"/>
+      <c r="AF18" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="AE16" s="105"/>
-      <c r="AF16" s="105"/>
-      <c r="AG16" s="105"/>
-      <c r="AH16" s="105"/>
-      <c r="AI16" s="105"/>
-      <c r="AJ16" s="105"/>
-      <c r="AK16" s="105"/>
-      <c r="AL16" s="105"/>
-      <c r="AM16" s="105"/>
-      <c r="AN16" s="105"/>
-      <c r="AO16" s="108"/>
-    </row>
-    <row r="17" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="19"/>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="160"/>
-      <c r="AE17" s="160"/>
-      <c r="AF17" s="160"/>
-      <c r="AG17" s="160"/>
-      <c r="AH17" s="160"/>
-      <c r="AI17" s="160"/>
-      <c r="AJ17" s="160"/>
-      <c r="AK17" s="160"/>
-      <c r="AL17" s="160"/>
-      <c r="AM17" s="160"/>
-      <c r="AN17" s="160"/>
-      <c r="AO17" s="161"/>
-    </row>
-    <row r="18" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="182" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="152"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="152"/>
-      <c r="K18" s="152"/>
-      <c r="L18" s="152"/>
-      <c r="M18" s="152"/>
-      <c r="N18" s="152"/>
-      <c r="O18" s="152"/>
-      <c r="P18" s="152"/>
-      <c r="Q18" s="152"/>
-      <c r="R18" s="152"/>
-      <c r="S18" s="152"/>
-      <c r="T18" s="152"/>
-      <c r="U18" s="152"/>
-      <c r="V18" s="152"/>
-      <c r="W18" s="152"/>
-      <c r="X18" s="152"/>
-      <c r="Y18" s="152"/>
-      <c r="Z18" s="152"/>
-      <c r="AA18" s="152"/>
-      <c r="AB18" s="152"/>
-      <c r="AC18" s="153"/>
-      <c r="AD18" s="107" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE18" s="105"/>
-      <c r="AF18" s="105"/>
       <c r="AG18" s="105"/>
       <c r="AH18" s="105"/>
       <c r="AI18" s="105"/>
@@ -3376,653 +3307,627 @@
       <c r="AL18" s="105"/>
       <c r="AM18" s="105"/>
       <c r="AN18" s="105"/>
-      <c r="AO18" s="108"/>
-    </row>
-    <row r="19" spans="1:41" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="154"/>
-      <c r="B19" s="155"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
-      <c r="L19" s="155"/>
-      <c r="M19" s="155"/>
-      <c r="N19" s="155"/>
-      <c r="O19" s="155"/>
-      <c r="P19" s="155"/>
-      <c r="Q19" s="155"/>
-      <c r="R19" s="155"/>
-      <c r="S19" s="155"/>
-      <c r="T19" s="155"/>
-      <c r="U19" s="155"/>
-      <c r="V19" s="155"/>
-      <c r="W19" s="155"/>
-      <c r="X19" s="155"/>
-      <c r="Y19" s="155"/>
-      <c r="Z19" s="155"/>
-      <c r="AA19" s="155"/>
-      <c r="AB19" s="155"/>
-      <c r="AC19" s="156"/>
-      <c r="AD19" s="44"/>
-      <c r="AE19" s="21" t="s">
+      <c r="AO18" s="105"/>
+      <c r="AP18" s="105"/>
+      <c r="AQ18" s="108"/>
+    </row>
+    <row r="19" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="19"/>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE19" s="11"/>
+      <c r="AF19" s="162"/>
+      <c r="AG19" s="162"/>
+      <c r="AH19" s="162"/>
+      <c r="AI19" s="162"/>
+      <c r="AJ19" s="162"/>
+      <c r="AK19" s="162"/>
+      <c r="AL19" s="162"/>
+      <c r="AM19" s="162"/>
+      <c r="AN19" s="162"/>
+      <c r="AO19" s="162"/>
+      <c r="AP19" s="162"/>
+      <c r="AQ19" s="163"/>
+    </row>
+    <row r="20" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C20" s="184" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="154"/>
+      <c r="E20" s="154"/>
+      <c r="F20" s="154"/>
+      <c r="G20" s="154"/>
+      <c r="H20" s="154"/>
+      <c r="I20" s="154"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="154"/>
+      <c r="L20" s="154"/>
+      <c r="M20" s="154"/>
+      <c r="N20" s="154"/>
+      <c r="O20" s="154"/>
+      <c r="P20" s="154"/>
+      <c r="Q20" s="154"/>
+      <c r="R20" s="154"/>
+      <c r="S20" s="154"/>
+      <c r="T20" s="154"/>
+      <c r="U20" s="154"/>
+      <c r="V20" s="154"/>
+      <c r="W20" s="154"/>
+      <c r="X20" s="154"/>
+      <c r="Y20" s="154"/>
+      <c r="Z20" s="154"/>
+      <c r="AA20" s="154"/>
+      <c r="AB20" s="154"/>
+      <c r="AC20" s="154"/>
+      <c r="AD20" s="154"/>
+      <c r="AE20" s="155"/>
+      <c r="AF20" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG20" s="105"/>
+      <c r="AH20" s="105"/>
+      <c r="AI20" s="105"/>
+      <c r="AJ20" s="105"/>
+      <c r="AK20" s="105"/>
+      <c r="AL20" s="105"/>
+      <c r="AM20" s="105"/>
+      <c r="AN20" s="105"/>
+      <c r="AO20" s="105"/>
+      <c r="AP20" s="105"/>
+      <c r="AQ20" s="108"/>
+    </row>
+    <row r="21" spans="3:43" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="156"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="157"/>
+      <c r="F21" s="157"/>
+      <c r="G21" s="157"/>
+      <c r="H21" s="157"/>
+      <c r="I21" s="157"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="157"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="157"/>
+      <c r="P21" s="157"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="157"/>
+      <c r="S21" s="157"/>
+      <c r="T21" s="157"/>
+      <c r="U21" s="157"/>
+      <c r="V21" s="157"/>
+      <c r="W21" s="157"/>
+      <c r="X21" s="157"/>
+      <c r="Y21" s="157"/>
+      <c r="Z21" s="157"/>
+      <c r="AA21" s="157"/>
+      <c r="AB21" s="157"/>
+      <c r="AC21" s="157"/>
+      <c r="AD21" s="157"/>
+      <c r="AE21" s="158"/>
+      <c r="AF21" s="44"/>
+      <c r="AG21" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="44"/>
-      <c r="AI19" s="21" t="s">
+      <c r="AH21" s="21"/>
+      <c r="AI21" s="21"/>
+      <c r="AJ21" s="44"/>
+      <c r="AK21" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="AJ19" s="21"/>
-      <c r="AK19" s="21"/>
-      <c r="AL19" s="44"/>
-      <c r="AM19" s="21" t="s">
+      <c r="AL21" s="21"/>
+      <c r="AM21" s="21"/>
+      <c r="AN21" s="44"/>
+      <c r="AO21" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="22"/>
-    </row>
-    <row r="20" spans="1:41" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="21" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="76" t="s">
+      <c r="AP21" s="21"/>
+      <c r="AQ21" s="22"/>
+    </row>
+    <row r="22" spans="3:43" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="23" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="77" t="s">
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="77"/>
+      <c r="M23" s="77"/>
+      <c r="N23" s="77"/>
+      <c r="O23" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="N21" s="77"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="77"/>
-      <c r="U21" s="77"/>
-      <c r="V21" s="77"/>
-      <c r="W21" s="77"/>
-      <c r="X21" s="77"/>
-      <c r="Y21" s="77"/>
-      <c r="Z21" s="77"/>
-      <c r="AA21" s="77"/>
-      <c r="AB21" s="77"/>
-      <c r="AC21" s="78"/>
-      <c r="AD21" s="79" t="s">
+      <c r="P23" s="77"/>
+      <c r="Q23" s="77"/>
+      <c r="R23" s="77"/>
+      <c r="S23" s="77"/>
+      <c r="T23" s="77"/>
+      <c r="U23" s="77"/>
+      <c r="V23" s="77"/>
+      <c r="W23" s="77"/>
+      <c r="X23" s="77"/>
+      <c r="Y23" s="77"/>
+      <c r="Z23" s="77"/>
+      <c r="AA23" s="77"/>
+      <c r="AB23" s="77"/>
+      <c r="AC23" s="77"/>
+      <c r="AD23" s="77"/>
+      <c r="AE23" s="78"/>
+      <c r="AF23" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AE21" s="80"/>
-      <c r="AF21" s="80"/>
-      <c r="AG21" s="80"/>
-      <c r="AH21" s="80"/>
-      <c r="AI21" s="80"/>
-      <c r="AJ21" s="80"/>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
-      <c r="AM21" s="80"/>
-      <c r="AN21" s="80"/>
-      <c r="AO21" s="81"/>
-    </row>
-    <row r="22" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="73" t="s">
+      <c r="AG23" s="80"/>
+      <c r="AH23" s="80"/>
+      <c r="AI23" s="80"/>
+      <c r="AJ23" s="80"/>
+      <c r="AK23" s="80"/>
+      <c r="AL23" s="80"/>
+      <c r="AM23" s="80"/>
+      <c r="AN23" s="80"/>
+      <c r="AO23" s="80"/>
+      <c r="AP23" s="80"/>
+      <c r="AQ23" s="81"/>
+    </row>
+    <row r="24" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C24" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="165" t="s">
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="165"/>
-      <c r="H22" s="165"/>
-      <c r="I22" s="165"/>
-      <c r="J22" s="165"/>
-      <c r="K22" s="165"/>
-      <c r="L22" s="165"/>
-      <c r="M22" s="165"/>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="165"/>
-      <c r="Q22" s="165"/>
-      <c r="R22" s="165"/>
-      <c r="S22" s="165"/>
-      <c r="T22" s="165"/>
-      <c r="U22" s="165"/>
-      <c r="V22" s="165"/>
-      <c r="W22" s="166"/>
-      <c r="X22" s="167" t="s">
+      <c r="I24" s="167"/>
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="167"/>
+      <c r="N24" s="167"/>
+      <c r="O24" s="167"/>
+      <c r="P24" s="167"/>
+      <c r="Q24" s="167"/>
+      <c r="R24" s="167"/>
+      <c r="S24" s="167"/>
+      <c r="T24" s="167"/>
+      <c r="U24" s="167"/>
+      <c r="V24" s="167"/>
+      <c r="W24" s="167"/>
+      <c r="X24" s="167"/>
+      <c r="Y24" s="168"/>
+      <c r="Z24" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="Y22" s="168"/>
-      <c r="Z22" s="168"/>
-      <c r="AA22" s="168"/>
-      <c r="AB22" s="168"/>
-      <c r="AC22" s="169"/>
-      <c r="AD22" s="2"/>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="43" t="s">
+      <c r="AA24" s="170"/>
+      <c r="AB24" s="170"/>
+      <c r="AC24" s="170"/>
+      <c r="AD24" s="170"/>
+      <c r="AE24" s="171"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG22" s="39" t="s">
+      <c r="AI24" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH22" s="40"/>
-      <c r="AI22" s="41"/>
-      <c r="AJ22" s="42"/>
-      <c r="AK22" s="43"/>
-      <c r="AL22" s="39" t="s">
+      <c r="AJ24" s="40"/>
+      <c r="AK24" s="41"/>
+      <c r="AL24" s="42"/>
+      <c r="AM24" s="43"/>
+      <c r="AN24" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM22" s="40"/>
-      <c r="AN22" s="14"/>
-      <c r="AO22" s="17"/>
-    </row>
-    <row r="23" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="162" t="s">
+      <c r="AO24" s="40"/>
+      <c r="AP24" s="14"/>
+      <c r="AQ24" s="17"/>
+    </row>
+    <row r="25" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C25" s="164" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="163"/>
-      <c r="C23" s="163"/>
-      <c r="D23" s="163"/>
-      <c r="E23" s="163"/>
-      <c r="F23" s="163"/>
-      <c r="G23" s="163"/>
-      <c r="H23" s="163"/>
-      <c r="I23" s="163"/>
-      <c r="J23" s="163"/>
-      <c r="K23" s="163"/>
-      <c r="L23" s="163"/>
-      <c r="M23" s="163"/>
-      <c r="N23" s="163"/>
-      <c r="O23" s="163"/>
-      <c r="P23" s="163"/>
-      <c r="Q23" s="163"/>
-      <c r="R23" s="163"/>
-      <c r="S23" s="163"/>
-      <c r="T23" s="163"/>
-      <c r="U23" s="163"/>
-      <c r="V23" s="163"/>
-      <c r="W23" s="164"/>
-      <c r="X23" s="170"/>
-      <c r="Y23" s="171"/>
-      <c r="Z23" s="171"/>
-      <c r="AA23" s="171"/>
-      <c r="AB23" s="171"/>
-      <c r="AC23" s="172"/>
-      <c r="AD23" s="107" t="s">
+      <c r="D25" s="165"/>
+      <c r="E25" s="165"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="165"/>
+      <c r="H25" s="165"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="165"/>
+      <c r="K25" s="165"/>
+      <c r="L25" s="165"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="165"/>
+      <c r="O25" s="165"/>
+      <c r="P25" s="165"/>
+      <c r="Q25" s="165"/>
+      <c r="R25" s="165"/>
+      <c r="S25" s="165"/>
+      <c r="T25" s="165"/>
+      <c r="U25" s="165"/>
+      <c r="V25" s="165"/>
+      <c r="W25" s="165"/>
+      <c r="X25" s="165"/>
+      <c r="Y25" s="166"/>
+      <c r="Z25" s="172"/>
+      <c r="AA25" s="173"/>
+      <c r="AB25" s="173"/>
+      <c r="AC25" s="173"/>
+      <c r="AD25" s="173"/>
+      <c r="AE25" s="174"/>
+      <c r="AF25" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="AE23" s="105"/>
-      <c r="AF23" s="105"/>
-      <c r="AG23" s="105"/>
-      <c r="AH23" s="105"/>
-      <c r="AI23" s="105"/>
-      <c r="AJ23" s="105"/>
-      <c r="AK23" s="105"/>
-      <c r="AL23" s="105"/>
-      <c r="AM23" s="105"/>
-      <c r="AN23" s="105"/>
-      <c r="AO23" s="108"/>
-    </row>
-    <row r="24" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="162" t="s">
+      <c r="AG25" s="105"/>
+      <c r="AH25" s="105"/>
+      <c r="AI25" s="105"/>
+      <c r="AJ25" s="105"/>
+      <c r="AK25" s="105"/>
+      <c r="AL25" s="105"/>
+      <c r="AM25" s="105"/>
+      <c r="AN25" s="105"/>
+      <c r="AO25" s="105"/>
+      <c r="AP25" s="105"/>
+      <c r="AQ25" s="108"/>
+    </row>
+    <row r="26" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C26" s="164" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="163"/>
-      <c r="C24" s="163"/>
-      <c r="D24" s="163"/>
-      <c r="E24" s="163"/>
-      <c r="F24" s="163"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="163"/>
-      <c r="I24" s="163"/>
-      <c r="J24" s="163"/>
-      <c r="K24" s="163"/>
-      <c r="L24" s="163"/>
-      <c r="M24" s="163"/>
-      <c r="N24" s="163"/>
-      <c r="O24" s="163"/>
-      <c r="P24" s="163"/>
-      <c r="Q24" s="163"/>
-      <c r="R24" s="163"/>
-      <c r="S24" s="163"/>
-      <c r="T24" s="163"/>
-      <c r="U24" s="163"/>
-      <c r="V24" s="163"/>
-      <c r="W24" s="164"/>
-      <c r="X24" s="170"/>
-      <c r="Y24" s="171"/>
-      <c r="Z24" s="171"/>
-      <c r="AA24" s="171"/>
-      <c r="AB24" s="171"/>
-      <c r="AC24" s="172"/>
-      <c r="AD24" s="107"/>
-      <c r="AE24" s="106"/>
-      <c r="AF24" s="107"/>
-      <c r="AG24" s="106"/>
-      <c r="AH24" s="107"/>
-      <c r="AI24" s="106"/>
-      <c r="AJ24" s="107"/>
-      <c r="AK24" s="106"/>
-      <c r="AL24" s="107"/>
-      <c r="AM24" s="106"/>
-      <c r="AN24" s="107"/>
-      <c r="AO24" s="106"/>
-    </row>
-    <row r="25" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="162" t="s">
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="165"/>
+      <c r="H26" s="165"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="165"/>
+      <c r="K26" s="165"/>
+      <c r="L26" s="165"/>
+      <c r="M26" s="165"/>
+      <c r="N26" s="165"/>
+      <c r="O26" s="165"/>
+      <c r="P26" s="165"/>
+      <c r="Q26" s="165"/>
+      <c r="R26" s="165"/>
+      <c r="S26" s="165"/>
+      <c r="T26" s="165"/>
+      <c r="U26" s="165"/>
+      <c r="V26" s="165"/>
+      <c r="W26" s="165"/>
+      <c r="X26" s="165"/>
+      <c r="Y26" s="166"/>
+      <c r="Z26" s="172"/>
+      <c r="AA26" s="173"/>
+      <c r="AB26" s="173"/>
+      <c r="AC26" s="173"/>
+      <c r="AD26" s="173"/>
+      <c r="AE26" s="174"/>
+      <c r="AF26" s="107"/>
+      <c r="AG26" s="106"/>
+      <c r="AH26" s="107"/>
+      <c r="AI26" s="106"/>
+      <c r="AJ26" s="107"/>
+      <c r="AK26" s="106"/>
+      <c r="AL26" s="107"/>
+      <c r="AM26" s="106"/>
+      <c r="AN26" s="107"/>
+      <c r="AO26" s="106"/>
+      <c r="AP26" s="107"/>
+      <c r="AQ26" s="106"/>
+    </row>
+    <row r="27" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C27" s="164" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="163"/>
-      <c r="C25" s="163"/>
-      <c r="D25" s="163"/>
-      <c r="E25" s="163"/>
-      <c r="F25" s="163"/>
-      <c r="G25" s="163"/>
-      <c r="H25" s="163"/>
-      <c r="I25" s="163"/>
-      <c r="J25" s="163"/>
-      <c r="K25" s="163"/>
-      <c r="L25" s="163"/>
-      <c r="M25" s="163"/>
-      <c r="N25" s="163"/>
-      <c r="O25" s="163"/>
-      <c r="P25" s="163"/>
-      <c r="Q25" s="163"/>
-      <c r="R25" s="163"/>
-      <c r="S25" s="163"/>
-      <c r="T25" s="163"/>
-      <c r="U25" s="163"/>
-      <c r="V25" s="163"/>
-      <c r="W25" s="164"/>
-      <c r="X25" s="170"/>
-      <c r="Y25" s="171"/>
-      <c r="Z25" s="171"/>
-      <c r="AA25" s="171"/>
-      <c r="AB25" s="171"/>
-      <c r="AC25" s="172"/>
-      <c r="AD25" s="107"/>
-      <c r="AE25" s="106"/>
-      <c r="AF25" s="107"/>
-      <c r="AG25" s="106"/>
-      <c r="AH25" s="107"/>
-      <c r="AI25" s="106"/>
-      <c r="AJ25" s="107"/>
-      <c r="AK25" s="106"/>
-      <c r="AL25" s="107"/>
-      <c r="AM25" s="106"/>
-      <c r="AN25" s="107"/>
-      <c r="AO25" s="106"/>
-    </row>
-    <row r="26" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="176" t="s">
+      <c r="D27" s="165"/>
+      <c r="E27" s="165"/>
+      <c r="F27" s="165"/>
+      <c r="G27" s="165"/>
+      <c r="H27" s="165"/>
+      <c r="I27" s="165"/>
+      <c r="J27" s="165"/>
+      <c r="K27" s="165"/>
+      <c r="L27" s="165"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="165"/>
+      <c r="O27" s="165"/>
+      <c r="P27" s="165"/>
+      <c r="Q27" s="165"/>
+      <c r="R27" s="165"/>
+      <c r="S27" s="165"/>
+      <c r="T27" s="165"/>
+      <c r="U27" s="165"/>
+      <c r="V27" s="165"/>
+      <c r="W27" s="165"/>
+      <c r="X27" s="165"/>
+      <c r="Y27" s="166"/>
+      <c r="Z27" s="172"/>
+      <c r="AA27" s="173"/>
+      <c r="AB27" s="173"/>
+      <c r="AC27" s="173"/>
+      <c r="AD27" s="173"/>
+      <c r="AE27" s="174"/>
+      <c r="AF27" s="107"/>
+      <c r="AG27" s="106"/>
+      <c r="AH27" s="107"/>
+      <c r="AI27" s="106"/>
+      <c r="AJ27" s="107"/>
+      <c r="AK27" s="106"/>
+      <c r="AL27" s="107"/>
+      <c r="AM27" s="106"/>
+      <c r="AN27" s="107"/>
+      <c r="AO27" s="106"/>
+      <c r="AP27" s="107"/>
+      <c r="AQ27" s="106"/>
+    </row>
+    <row r="28" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C28" s="178" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="177"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="177"/>
-      <c r="F26" s="177"/>
-      <c r="G26" s="177"/>
-      <c r="H26" s="177"/>
-      <c r="I26" s="177"/>
-      <c r="J26" s="177"/>
-      <c r="K26" s="177"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="177"/>
-      <c r="N26" s="177"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="177"/>
-      <c r="Q26" s="177"/>
-      <c r="R26" s="177"/>
-      <c r="S26" s="177"/>
-      <c r="T26" s="177"/>
-      <c r="U26" s="177"/>
-      <c r="V26" s="177"/>
-      <c r="W26" s="178"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="174"/>
-      <c r="Z26" s="174"/>
-      <c r="AA26" s="174"/>
-      <c r="AB26" s="174"/>
-      <c r="AC26" s="175"/>
-      <c r="AD26" s="54"/>
-      <c r="AE26" s="7"/>
-      <c r="AF26" s="7"/>
-      <c r="AG26" s="7"/>
-      <c r="AH26" s="7"/>
-      <c r="AI26" s="7"/>
-      <c r="AJ26" s="7"/>
-      <c r="AK26" s="7"/>
-      <c r="AL26" s="7"/>
-      <c r="AM26" s="7"/>
-      <c r="AN26" s="7"/>
-      <c r="AO26" s="55"/>
-    </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A27" s="135" t="s">
+      <c r="D28" s="179"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="179"/>
+      <c r="I28" s="179"/>
+      <c r="J28" s="179"/>
+      <c r="K28" s="179"/>
+      <c r="L28" s="179"/>
+      <c r="M28" s="179"/>
+      <c r="N28" s="179"/>
+      <c r="O28" s="179"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="179"/>
+      <c r="R28" s="179"/>
+      <c r="S28" s="179"/>
+      <c r="T28" s="179"/>
+      <c r="U28" s="179"/>
+      <c r="V28" s="179"/>
+      <c r="W28" s="179"/>
+      <c r="X28" s="179"/>
+      <c r="Y28" s="180"/>
+      <c r="Z28" s="175"/>
+      <c r="AA28" s="176"/>
+      <c r="AB28" s="176"/>
+      <c r="AC28" s="176"/>
+      <c r="AD28" s="176"/>
+      <c r="AE28" s="177"/>
+      <c r="AF28" s="54"/>
+      <c r="AG28" s="7"/>
+      <c r="AH28" s="7"/>
+      <c r="AI28" s="7"/>
+      <c r="AJ28" s="7"/>
+      <c r="AK28" s="7"/>
+      <c r="AL28" s="7"/>
+      <c r="AM28" s="7"/>
+      <c r="AN28" s="7"/>
+      <c r="AO28" s="7"/>
+      <c r="AP28" s="7"/>
+      <c r="AQ28" s="55"/>
+    </row>
+    <row r="29" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C29" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="152"/>
-      <c r="O27" s="152"/>
-      <c r="P27" s="152"/>
-      <c r="Q27" s="152"/>
-      <c r="R27" s="152"/>
-      <c r="S27" s="152"/>
-      <c r="T27" s="152"/>
-      <c r="U27" s="152"/>
-      <c r="V27" s="152"/>
-      <c r="W27" s="152"/>
-      <c r="X27" s="152"/>
-      <c r="Y27" s="152"/>
-      <c r="Z27" s="152"/>
-      <c r="AA27" s="152"/>
-      <c r="AB27" s="152"/>
-      <c r="AC27" s="153"/>
-      <c r="AD27" s="107" t="s">
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="154"/>
+      <c r="O29" s="154"/>
+      <c r="P29" s="154"/>
+      <c r="Q29" s="154"/>
+      <c r="R29" s="154"/>
+      <c r="S29" s="154"/>
+      <c r="T29" s="154"/>
+      <c r="U29" s="154"/>
+      <c r="V29" s="154"/>
+      <c r="W29" s="154"/>
+      <c r="X29" s="154"/>
+      <c r="Y29" s="154"/>
+      <c r="Z29" s="154"/>
+      <c r="AA29" s="154"/>
+      <c r="AB29" s="154"/>
+      <c r="AC29" s="154"/>
+      <c r="AD29" s="154"/>
+      <c r="AE29" s="155"/>
+      <c r="AF29" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="AE27" s="105"/>
-      <c r="AF27" s="105"/>
-      <c r="AG27" s="105"/>
-      <c r="AH27" s="105"/>
-      <c r="AI27" s="105"/>
-      <c r="AJ27" s="105"/>
-      <c r="AK27" s="105"/>
-      <c r="AL27" s="105"/>
-      <c r="AM27" s="105"/>
-      <c r="AN27" s="105"/>
-      <c r="AO27" s="108"/>
-    </row>
-    <row r="28" spans="1:41" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="154"/>
-      <c r="B28" s="155"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="155"/>
-      <c r="F28" s="155"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="155"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="155"/>
-      <c r="L28" s="155"/>
-      <c r="M28" s="155"/>
-      <c r="N28" s="155"/>
-      <c r="O28" s="155"/>
-      <c r="P28" s="155"/>
-      <c r="Q28" s="155"/>
-      <c r="R28" s="155"/>
-      <c r="S28" s="155"/>
-      <c r="T28" s="155"/>
-      <c r="U28" s="155"/>
-      <c r="V28" s="155"/>
-      <c r="W28" s="155"/>
-      <c r="X28" s="155"/>
-      <c r="Y28" s="155"/>
-      <c r="Z28" s="155"/>
-      <c r="AA28" s="155"/>
-      <c r="AB28" s="155"/>
-      <c r="AC28" s="156"/>
-      <c r="AD28" s="44"/>
-      <c r="AE28" s="21" t="s">
+      <c r="AG29" s="105"/>
+      <c r="AH29" s="105"/>
+      <c r="AI29" s="105"/>
+      <c r="AJ29" s="105"/>
+      <c r="AK29" s="105"/>
+      <c r="AL29" s="105"/>
+      <c r="AM29" s="105"/>
+      <c r="AN29" s="105"/>
+      <c r="AO29" s="105"/>
+      <c r="AP29" s="105"/>
+      <c r="AQ29" s="108"/>
+    </row>
+    <row r="30" spans="3:43" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C30" s="156"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
+      <c r="O30" s="157"/>
+      <c r="P30" s="157"/>
+      <c r="Q30" s="157"/>
+      <c r="R30" s="157"/>
+      <c r="S30" s="157"/>
+      <c r="T30" s="157"/>
+      <c r="U30" s="157"/>
+      <c r="V30" s="157"/>
+      <c r="W30" s="157"/>
+      <c r="X30" s="157"/>
+      <c r="Y30" s="157"/>
+      <c r="Z30" s="157"/>
+      <c r="AA30" s="157"/>
+      <c r="AB30" s="157"/>
+      <c r="AC30" s="157"/>
+      <c r="AD30" s="157"/>
+      <c r="AE30" s="158"/>
+      <c r="AF30" s="44"/>
+      <c r="AG30" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="AF28" s="21"/>
-      <c r="AG28" s="21"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="21" t="s">
+      <c r="AH30" s="21"/>
+      <c r="AI30" s="21"/>
+      <c r="AJ30" s="44"/>
+      <c r="AK30" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="AJ28" s="21"/>
-      <c r="AK28" s="21"/>
-      <c r="AL28" s="44"/>
-      <c r="AM28" s="21" t="s">
+      <c r="AL30" s="21"/>
+      <c r="AM30" s="21"/>
+      <c r="AN30" s="44"/>
+      <c r="AO30" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="AN28" s="21"/>
-      <c r="AO28" s="22"/>
-    </row>
-    <row r="29" spans="1:41" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="30" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="157" t="s">
+      <c r="AP30" s="21"/>
+      <c r="AQ30" s="22"/>
+    </row>
+    <row r="31" spans="3:43" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="32" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="159" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="158"/>
-      <c r="C30" s="158"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="N30" s="158"/>
-      <c r="O30" s="158"/>
-      <c r="P30" s="158"/>
-      <c r="Q30" s="158"/>
-      <c r="R30" s="158"/>
-      <c r="S30" s="158"/>
-      <c r="T30" s="158"/>
-      <c r="U30" s="158"/>
-      <c r="V30" s="158"/>
-      <c r="W30" s="158"/>
-      <c r="X30" s="158"/>
-      <c r="Y30" s="158"/>
-      <c r="Z30" s="158"/>
-      <c r="AA30" s="158"/>
-      <c r="AB30" s="158"/>
-      <c r="AC30" s="159"/>
-      <c r="AD30" s="79" t="s">
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="160"/>
+      <c r="L32" s="160"/>
+      <c r="M32" s="160"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="160"/>
+      <c r="P32" s="160"/>
+      <c r="Q32" s="160"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="160"/>
+      <c r="T32" s="160"/>
+      <c r="U32" s="160"/>
+      <c r="V32" s="160"/>
+      <c r="W32" s="160"/>
+      <c r="X32" s="160"/>
+      <c r="Y32" s="160"/>
+      <c r="Z32" s="160"/>
+      <c r="AA32" s="160"/>
+      <c r="AB32" s="160"/>
+      <c r="AC32" s="160"/>
+      <c r="AD32" s="160"/>
+      <c r="AE32" s="161"/>
+      <c r="AF32" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AE30" s="80"/>
-      <c r="AF30" s="80"/>
-      <c r="AG30" s="80"/>
-      <c r="AH30" s="80"/>
-      <c r="AI30" s="80"/>
-      <c r="AJ30" s="80"/>
-      <c r="AK30" s="80"/>
-      <c r="AL30" s="80"/>
-      <c r="AM30" s="80"/>
-      <c r="AN30" s="80"/>
-      <c r="AO30" s="81"/>
-    </row>
-    <row r="31" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="66" t="e">
+      <c r="AG32" s="80"/>
+      <c r="AH32" s="80"/>
+      <c r="AI32" s="80"/>
+      <c r="AJ32" s="80"/>
+      <c r="AK32" s="80"/>
+      <c r="AL32" s="80"/>
+      <c r="AM32" s="80"/>
+      <c r="AN32" s="80"/>
+      <c r="AO32" s="80"/>
+      <c r="AP32" s="80"/>
+      <c r="AQ32" s="81"/>
+    </row>
+    <row r="33" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C33" s="66" t="e">
         <f>IF(#REF!="X","Embutidos FTK e chapas inox estão com dimensionais e posições conforme pré-estabelecido","Embutidos FTK  estão com dimensionais e posições conforme pré-estabelecido")</f>
         <v>#REF!</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="7"/>
-      <c r="AC31" s="8"/>
-      <c r="AD31" s="3"/>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="43" t="s">
+      <c r="D33" s="15"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
+      <c r="AA33" s="7"/>
+      <c r="AB33" s="7"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="7"/>
+      <c r="AE33" s="8"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG31" s="39" t="s">
+      <c r="AI33" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH31" s="40"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="42"/>
-      <c r="AK31" s="43"/>
-      <c r="AL31" s="39" t="s">
+      <c r="AJ33" s="40"/>
+      <c r="AK33" s="41"/>
+      <c r="AL33" s="42"/>
+      <c r="AM33" s="43"/>
+      <c r="AN33" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM31" s="40"/>
-      <c r="AN31" s="14"/>
-      <c r="AO31" s="17"/>
-    </row>
-    <row r="32" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="65" t="s">
+      <c r="AO33" s="40"/>
+      <c r="AP33" s="14"/>
+      <c r="AQ33" s="17"/>
+    </row>
+    <row r="34" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C34" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="105" t="s">
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="AE34" s="11"/>
+      <c r="AF34" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="AE32" s="105"/>
-      <c r="AF32" s="105"/>
-      <c r="AG32" s="105"/>
-      <c r="AH32" s="105"/>
-      <c r="AI32" s="105"/>
-      <c r="AJ32" s="105"/>
-      <c r="AK32" s="105"/>
-      <c r="AL32" s="105"/>
-      <c r="AM32" s="105"/>
-      <c r="AN32" s="105"/>
-      <c r="AO32" s="108"/>
-    </row>
-    <row r="33" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="64" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="X33" s="12"/>
-      <c r="Y33" s="12"/>
-      <c r="Z33" s="12"/>
-      <c r="AA33" s="12"/>
-      <c r="AB33" s="12"/>
-      <c r="AC33" s="13"/>
-      <c r="AD33" s="106"/>
-      <c r="AE33" s="160"/>
-      <c r="AF33" s="160"/>
-      <c r="AG33" s="160"/>
-      <c r="AH33" s="160"/>
-      <c r="AI33" s="160"/>
-      <c r="AJ33" s="160"/>
-      <c r="AK33" s="160"/>
-      <c r="AL33" s="160"/>
-      <c r="AM33" s="160"/>
-      <c r="AN33" s="160"/>
-      <c r="AO33" s="161"/>
-    </row>
-    <row r="34" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="149" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="129"/>
-      <c r="C34" s="129"/>
-      <c r="D34" s="129"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="129"/>
-      <c r="G34" s="129"/>
-      <c r="H34" s="129"/>
-      <c r="I34" s="150"/>
-      <c r="J34" s="150"/>
-      <c r="K34" s="150"/>
-      <c r="L34" s="150"/>
-      <c r="M34" s="150"/>
-      <c r="N34" s="150"/>
-      <c r="O34" s="150"/>
-      <c r="P34" s="150"/>
-      <c r="Q34" s="150"/>
-      <c r="R34" s="150"/>
-      <c r="S34" s="150"/>
-      <c r="T34" s="150"/>
-      <c r="U34" s="150"/>
-      <c r="V34" s="150"/>
-      <c r="W34" s="150"/>
-      <c r="X34" s="150"/>
-      <c r="Y34" s="150"/>
-      <c r="Z34" s="150"/>
-      <c r="AA34" s="150"/>
-      <c r="AB34" s="150"/>
-      <c r="AC34" s="151"/>
-      <c r="AD34" s="107" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE34" s="105"/>
-      <c r="AF34" s="105"/>
       <c r="AG34" s="105"/>
       <c r="AH34" s="105"/>
       <c r="AI34" s="105"/>
@@ -4031,276 +3936,313 @@
       <c r="AL34" s="105"/>
       <c r="AM34" s="105"/>
       <c r="AN34" s="105"/>
-      <c r="AO34" s="108"/>
-    </row>
-    <row r="35" spans="1:69" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="154"/>
-      <c r="B35" s="155"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="155"/>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="155"/>
-      <c r="J35" s="155"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="155"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-      <c r="O35" s="155"/>
-      <c r="P35" s="155"/>
-      <c r="Q35" s="155"/>
-      <c r="R35" s="155"/>
-      <c r="S35" s="155"/>
-      <c r="T35" s="155"/>
-      <c r="U35" s="155"/>
-      <c r="V35" s="155"/>
-      <c r="W35" s="155"/>
-      <c r="X35" s="155"/>
-      <c r="Y35" s="155"/>
-      <c r="Z35" s="155"/>
-      <c r="AA35" s="155"/>
-      <c r="AB35" s="155"/>
-      <c r="AC35" s="156"/>
-      <c r="AD35" s="44"/>
-      <c r="AE35" s="21" t="s">
+      <c r="AO34" s="105"/>
+      <c r="AP34" s="105"/>
+      <c r="AQ34" s="108"/>
+    </row>
+    <row r="35" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C35" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="12"/>
+      <c r="Z35" s="12"/>
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="12"/>
+      <c r="AC35" s="12"/>
+      <c r="AD35" s="12"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="106"/>
+      <c r="AG35" s="162"/>
+      <c r="AH35" s="162"/>
+      <c r="AI35" s="162"/>
+      <c r="AJ35" s="162"/>
+      <c r="AK35" s="162"/>
+      <c r="AL35" s="162"/>
+      <c r="AM35" s="162"/>
+      <c r="AN35" s="162"/>
+      <c r="AO35" s="162"/>
+      <c r="AP35" s="162"/>
+      <c r="AQ35" s="163"/>
+    </row>
+    <row r="36" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="131"/>
+      <c r="E36" s="131"/>
+      <c r="F36" s="131"/>
+      <c r="G36" s="131"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="131"/>
+      <c r="K36" s="152"/>
+      <c r="L36" s="152"/>
+      <c r="M36" s="152"/>
+      <c r="N36" s="152"/>
+      <c r="O36" s="152"/>
+      <c r="P36" s="152"/>
+      <c r="Q36" s="152"/>
+      <c r="R36" s="152"/>
+      <c r="S36" s="152"/>
+      <c r="T36" s="152"/>
+      <c r="U36" s="152"/>
+      <c r="V36" s="152"/>
+      <c r="W36" s="152"/>
+      <c r="X36" s="152"/>
+      <c r="Y36" s="152"/>
+      <c r="Z36" s="152"/>
+      <c r="AA36" s="152"/>
+      <c r="AB36" s="152"/>
+      <c r="AC36" s="152"/>
+      <c r="AD36" s="152"/>
+      <c r="AE36" s="153"/>
+      <c r="AF36" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG36" s="105"/>
+      <c r="AH36" s="105"/>
+      <c r="AI36" s="105"/>
+      <c r="AJ36" s="105"/>
+      <c r="AK36" s="105"/>
+      <c r="AL36" s="105"/>
+      <c r="AM36" s="105"/>
+      <c r="AN36" s="105"/>
+      <c r="AO36" s="105"/>
+      <c r="AP36" s="105"/>
+      <c r="AQ36" s="108"/>
+    </row>
+    <row r="37" spans="3:71" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C37" s="156"/>
+      <c r="D37" s="157"/>
+      <c r="E37" s="157"/>
+      <c r="F37" s="157"/>
+      <c r="G37" s="157"/>
+      <c r="H37" s="157"/>
+      <c r="I37" s="157"/>
+      <c r="J37" s="157"/>
+      <c r="K37" s="157"/>
+      <c r="L37" s="157"/>
+      <c r="M37" s="157"/>
+      <c r="N37" s="157"/>
+      <c r="O37" s="157"/>
+      <c r="P37" s="157"/>
+      <c r="Q37" s="157"/>
+      <c r="R37" s="157"/>
+      <c r="S37" s="157"/>
+      <c r="T37" s="157"/>
+      <c r="U37" s="157"/>
+      <c r="V37" s="157"/>
+      <c r="W37" s="157"/>
+      <c r="X37" s="157"/>
+      <c r="Y37" s="157"/>
+      <c r="Z37" s="157"/>
+      <c r="AA37" s="157"/>
+      <c r="AB37" s="157"/>
+      <c r="AC37" s="157"/>
+      <c r="AD37" s="157"/>
+      <c r="AE37" s="158"/>
+      <c r="AF37" s="44"/>
+      <c r="AG37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="AF35" s="21"/>
-      <c r="AG35" s="21"/>
-      <c r="AH35" s="44"/>
-      <c r="AI35" s="21" t="s">
+      <c r="AH37" s="21"/>
+      <c r="AI37" s="21"/>
+      <c r="AJ37" s="44"/>
+      <c r="AK37" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="AJ35" s="21"/>
-      <c r="AK35" s="21"/>
-      <c r="AL35" s="44"/>
-      <c r="AM35" s="21" t="s">
+      <c r="AL37" s="21"/>
+      <c r="AM37" s="21"/>
+      <c r="AN37" s="44"/>
+      <c r="AO37" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="AN35" s="21"/>
-      <c r="AO35" s="22"/>
-    </row>
-    <row r="36" spans="1:69" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="37" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="144" t="s">
+      <c r="AP37" s="21"/>
+      <c r="AQ37" s="22"/>
+    </row>
+    <row r="38" spans="3:71" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="39" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C39" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="145"/>
-      <c r="C37" s="145"/>
-      <c r="D37" s="145"/>
-      <c r="E37" s="145"/>
-      <c r="F37" s="145"/>
-      <c r="G37" s="145"/>
-      <c r="H37" s="145"/>
-      <c r="I37" s="145"/>
-      <c r="J37" s="145"/>
-      <c r="K37" s="145"/>
-      <c r="L37" s="146" t="s">
+      <c r="D39" s="147"/>
+      <c r="E39" s="147"/>
+      <c r="F39" s="147"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="147"/>
+      <c r="J39" s="147"/>
+      <c r="K39" s="147"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="147"/>
+      <c r="N39" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="M37" s="147"/>
-      <c r="N37" s="147"/>
-      <c r="O37" s="80">
+      <c r="O39" s="149"/>
+      <c r="P39" s="149"/>
+      <c r="Q39" s="80">
         <v>12.7</v>
       </c>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="80"/>
-      <c r="R37" s="80" t="s">
+      <c r="R39" s="80"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="S37" s="80"/>
-      <c r="T37" s="148"/>
-      <c r="U37" s="146" t="s">
+      <c r="U39" s="80"/>
+      <c r="V39" s="150"/>
+      <c r="W39" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="V37" s="147"/>
-      <c r="W37" s="147"/>
-      <c r="X37" s="147"/>
-      <c r="Y37" s="147"/>
-      <c r="Z37" s="147"/>
-      <c r="AA37" s="80" t="s">
+      <c r="X39" s="149"/>
+      <c r="Y39" s="149"/>
+      <c r="Z39" s="149"/>
+      <c r="AA39" s="149"/>
+      <c r="AB39" s="149"/>
+      <c r="AC39" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="AB37" s="80"/>
-      <c r="AC37" s="80"/>
-      <c r="AD37" s="80"/>
-      <c r="AE37" s="80"/>
-      <c r="AF37" s="80"/>
-      <c r="AG37" s="80"/>
-      <c r="AH37" s="80"/>
-      <c r="AI37" s="80"/>
-      <c r="AJ37" s="80"/>
-      <c r="AK37" s="80"/>
-      <c r="AL37" s="80"/>
-      <c r="AM37" s="80"/>
-      <c r="AN37" s="80"/>
-      <c r="AO37" s="81"/>
-    </row>
-    <row r="38" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="135" t="s">
+      <c r="AD39" s="80"/>
+      <c r="AE39" s="80"/>
+      <c r="AF39" s="80"/>
+      <c r="AG39" s="80"/>
+      <c r="AH39" s="80"/>
+      <c r="AI39" s="80"/>
+      <c r="AJ39" s="80"/>
+      <c r="AK39" s="80"/>
+      <c r="AL39" s="80"/>
+      <c r="AM39" s="80"/>
+      <c r="AN39" s="80"/>
+      <c r="AO39" s="80"/>
+      <c r="AP39" s="80"/>
+      <c r="AQ39" s="81"/>
+    </row>
+    <row r="40" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C40" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="126"/>
-      <c r="C38" s="126"/>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="126"/>
-      <c r="H38" s="126"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="127"/>
-      <c r="L38" s="125" t="s">
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="128"/>
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="129"/>
+      <c r="N40" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="M38" s="126"/>
-      <c r="N38" s="126"/>
-      <c r="O38" s="126"/>
-      <c r="P38" s="126"/>
-      <c r="Q38" s="126"/>
-      <c r="R38" s="126"/>
-      <c r="S38" s="126"/>
-      <c r="T38" s="127"/>
-      <c r="U38" s="125" t="s">
+      <c r="O40" s="128"/>
+      <c r="P40" s="128"/>
+      <c r="Q40" s="128"/>
+      <c r="R40" s="128"/>
+      <c r="S40" s="128"/>
+      <c r="T40" s="128"/>
+      <c r="U40" s="128"/>
+      <c r="V40" s="129"/>
+      <c r="W40" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="V38" s="126"/>
-      <c r="W38" s="126"/>
-      <c r="X38" s="126"/>
-      <c r="Y38" s="126"/>
-      <c r="Z38" s="126"/>
-      <c r="AA38" s="126"/>
-      <c r="AB38" s="126"/>
-      <c r="AC38" s="126"/>
-      <c r="AD38" s="126"/>
-      <c r="AE38" s="127"/>
-      <c r="AF38" s="125" t="s">
+      <c r="X40" s="128"/>
+      <c r="Y40" s="128"/>
+      <c r="Z40" s="128"/>
+      <c r="AA40" s="128"/>
+      <c r="AB40" s="128"/>
+      <c r="AC40" s="128"/>
+      <c r="AD40" s="128"/>
+      <c r="AE40" s="128"/>
+      <c r="AF40" s="128"/>
+      <c r="AG40" s="129"/>
+      <c r="AH40" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="AG38" s="126"/>
-      <c r="AH38" s="126"/>
-      <c r="AI38" s="126"/>
-      <c r="AJ38" s="126"/>
-      <c r="AK38" s="126"/>
-      <c r="AL38" s="126"/>
-      <c r="AM38" s="126"/>
-      <c r="AN38" s="126"/>
-      <c r="AO38" s="136"/>
-    </row>
-    <row r="39" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="137" t="s">
+      <c r="AI40" s="128"/>
+      <c r="AJ40" s="128"/>
+      <c r="AK40" s="128"/>
+      <c r="AL40" s="128"/>
+      <c r="AM40" s="128"/>
+      <c r="AN40" s="128"/>
+      <c r="AO40" s="128"/>
+      <c r="AP40" s="128"/>
+      <c r="AQ40" s="138"/>
+    </row>
+    <row r="41" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C41" s="139" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="138"/>
-      <c r="C39" s="138"/>
-      <c r="D39" s="138"/>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="139"/>
-      <c r="L39" s="140" t="s">
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="140"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="140"/>
+      <c r="K41" s="140"/>
+      <c r="L41" s="140"/>
+      <c r="M41" s="141"/>
+      <c r="N41" s="142" t="s">
         <v>135</v>
       </c>
-      <c r="M39" s="141"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="141"/>
-      <c r="P39" s="141"/>
-      <c r="Q39" s="141"/>
-      <c r="R39" s="141"/>
-      <c r="S39" s="141"/>
-      <c r="T39" s="142"/>
-      <c r="U39" s="123" t="s">
+      <c r="O41" s="143"/>
+      <c r="P41" s="143"/>
+      <c r="Q41" s="143"/>
+      <c r="R41" s="143"/>
+      <c r="S41" s="143"/>
+      <c r="T41" s="143"/>
+      <c r="U41" s="143"/>
+      <c r="V41" s="144"/>
+      <c r="W41" s="125" t="s">
         <v>136</v>
       </c>
-      <c r="V39" s="123"/>
-      <c r="W39" s="123"/>
-      <c r="X39" s="123"/>
-      <c r="Y39" s="123"/>
-      <c r="Z39" s="123"/>
-      <c r="AA39" s="123"/>
-      <c r="AB39" s="123"/>
-      <c r="AC39" s="123"/>
-      <c r="AD39" s="123"/>
-      <c r="AE39" s="124"/>
-      <c r="AF39" s="140" t="s">
+      <c r="X41" s="125"/>
+      <c r="Y41" s="125"/>
+      <c r="Z41" s="125"/>
+      <c r="AA41" s="125"/>
+      <c r="AB41" s="125"/>
+      <c r="AC41" s="125"/>
+      <c r="AD41" s="125"/>
+      <c r="AE41" s="125"/>
+      <c r="AF41" s="125"/>
+      <c r="AG41" s="126"/>
+      <c r="AH41" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="AG39" s="141"/>
-      <c r="AH39" s="141"/>
-      <c r="AI39" s="141"/>
-      <c r="AJ39" s="141"/>
-      <c r="AK39" s="141"/>
-      <c r="AL39" s="141"/>
-      <c r="AM39" s="141"/>
-      <c r="AN39" s="141"/>
-      <c r="AO39" s="143"/>
-    </row>
-    <row r="40" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="104" t="s">
+      <c r="AI41" s="143"/>
+      <c r="AJ41" s="143"/>
+      <c r="AK41" s="143"/>
+      <c r="AL41" s="143"/>
+      <c r="AM41" s="143"/>
+      <c r="AN41" s="143"/>
+      <c r="AO41" s="143"/>
+      <c r="AP41" s="143"/>
+      <c r="AQ41" s="145"/>
+    </row>
+    <row r="42" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C42" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="105"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
-      <c r="K40" s="105"/>
-      <c r="L40" s="131" t="s">
-        <v>138</v>
-      </c>
-      <c r="M40" s="132"/>
-      <c r="N40" s="132"/>
-      <c r="O40" s="132"/>
-      <c r="P40" s="132"/>
-      <c r="Q40" s="132"/>
-      <c r="R40" s="132"/>
-      <c r="S40" s="132"/>
-      <c r="T40" s="133"/>
-      <c r="U40" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="V40" s="105"/>
-      <c r="W40" s="105"/>
-      <c r="X40" s="105"/>
-      <c r="Y40" s="105"/>
-      <c r="Z40" s="105"/>
-      <c r="AA40" s="105"/>
-      <c r="AB40" s="105"/>
-      <c r="AC40" s="105"/>
-      <c r="AD40" s="105"/>
-      <c r="AE40" s="105"/>
-      <c r="AF40" s="90" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG40" s="90"/>
-      <c r="AH40" s="90"/>
-      <c r="AI40" s="90"/>
-      <c r="AJ40" s="90"/>
-      <c r="AK40" s="90"/>
-      <c r="AL40" s="90"/>
-      <c r="AM40" s="90"/>
-      <c r="AN40" s="90"/>
-      <c r="AO40" s="134"/>
-    </row>
-    <row r="41" spans="1:69" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="19"/>
-      <c r="AO41" s="23"/>
-    </row>
-    <row r="42" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="32"/>
-      <c r="B42" s="105" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" s="105"/>
       <c r="D42" s="105"/>
       <c r="E42" s="105"/>
       <c r="F42" s="105"/>
@@ -4311,16 +4253,20 @@
       <c r="K42" s="105"/>
       <c r="L42" s="105"/>
       <c r="M42" s="105"/>
-      <c r="N42" s="105"/>
-      <c r="O42" s="105"/>
-      <c r="P42" s="105"/>
-      <c r="Q42" s="105"/>
-      <c r="R42" s="105"/>
-      <c r="S42" s="105"/>
-      <c r="T42" s="105"/>
-      <c r="U42" s="105"/>
-      <c r="V42" s="105"/>
-      <c r="W42" s="105"/>
+      <c r="N42" s="133" t="s">
+        <v>138</v>
+      </c>
+      <c r="O42" s="134"/>
+      <c r="P42" s="134"/>
+      <c r="Q42" s="134"/>
+      <c r="R42" s="134"/>
+      <c r="S42" s="134"/>
+      <c r="T42" s="134"/>
+      <c r="U42" s="134"/>
+      <c r="V42" s="135"/>
+      <c r="W42" s="107" t="s">
+        <v>60</v>
+      </c>
       <c r="X42" s="105"/>
       <c r="Y42" s="105"/>
       <c r="Z42" s="105"/>
@@ -4331,1074 +4277,1023 @@
       <c r="AE42" s="105"/>
       <c r="AF42" s="105"/>
       <c r="AG42" s="105"/>
-      <c r="AH42" s="105"/>
-      <c r="AI42" s="105"/>
-      <c r="AJ42" s="105"/>
-      <c r="AK42" s="105"/>
-      <c r="AL42" s="105"/>
-      <c r="AM42" s="105"/>
-      <c r="AN42" s="105"/>
-      <c r="AO42" s="17"/>
-    </row>
-    <row r="43" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="19"/>
-      <c r="B43" s="128" t="s">
+      <c r="AH42" s="90" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI42" s="90"/>
+      <c r="AJ42" s="90"/>
+      <c r="AK42" s="90"/>
+      <c r="AL42" s="90"/>
+      <c r="AM42" s="90"/>
+      <c r="AN42" s="90"/>
+      <c r="AO42" s="90"/>
+      <c r="AP42" s="90"/>
+      <c r="AQ42" s="136"/>
+    </row>
+    <row r="43" spans="3:71" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C43" s="19"/>
+      <c r="AQ43" s="23"/>
+    </row>
+    <row r="44" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C44" s="32"/>
+      <c r="D44" s="105" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="105"/>
+      <c r="M44" s="105"/>
+      <c r="N44" s="105"/>
+      <c r="O44" s="105"/>
+      <c r="P44" s="105"/>
+      <c r="Q44" s="105"/>
+      <c r="R44" s="105"/>
+      <c r="S44" s="105"/>
+      <c r="T44" s="105"/>
+      <c r="U44" s="105"/>
+      <c r="V44" s="105"/>
+      <c r="W44" s="105"/>
+      <c r="X44" s="105"/>
+      <c r="Y44" s="105"/>
+      <c r="Z44" s="105"/>
+      <c r="AA44" s="105"/>
+      <c r="AB44" s="105"/>
+      <c r="AC44" s="105"/>
+      <c r="AD44" s="105"/>
+      <c r="AE44" s="105"/>
+      <c r="AF44" s="105"/>
+      <c r="AG44" s="105"/>
+      <c r="AH44" s="105"/>
+      <c r="AI44" s="105"/>
+      <c r="AJ44" s="105"/>
+      <c r="AK44" s="105"/>
+      <c r="AL44" s="105"/>
+      <c r="AM44" s="105"/>
+      <c r="AN44" s="105"/>
+      <c r="AO44" s="105"/>
+      <c r="AP44" s="105"/>
+      <c r="AQ44" s="17"/>
+    </row>
+    <row r="45" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C45" s="19"/>
+      <c r="D45" s="130" t="s">
         <v>199</v>
       </c>
-      <c r="C43" s="129"/>
-      <c r="D43" s="130"/>
-      <c r="E43" s="128" t="s">
+      <c r="E45" s="131"/>
+      <c r="F45" s="132"/>
+      <c r="G45" s="130" t="s">
         <v>200</v>
       </c>
-      <c r="F43" s="129"/>
-      <c r="G43" s="130"/>
-      <c r="H43" s="128" t="s">
+      <c r="H45" s="131"/>
+      <c r="I45" s="132"/>
+      <c r="J45" s="130" t="s">
         <v>201</v>
       </c>
-      <c r="I43" s="129"/>
-      <c r="J43" s="130"/>
-      <c r="K43" s="128" t="s">
+      <c r="K45" s="131"/>
+      <c r="L45" s="132"/>
+      <c r="M45" s="130" t="s">
         <v>202</v>
       </c>
-      <c r="L43" s="129"/>
-      <c r="M43" s="130"/>
-      <c r="N43" s="128" t="s">
+      <c r="N45" s="131"/>
+      <c r="O45" s="132"/>
+      <c r="P45" s="130" t="s">
         <v>203</v>
       </c>
-      <c r="O43" s="129"/>
-      <c r="P43" s="130"/>
-      <c r="Q43" s="128" t="s">
+      <c r="Q45" s="131"/>
+      <c r="R45" s="132"/>
+      <c r="S45" s="130" t="s">
         <v>204</v>
       </c>
-      <c r="R43" s="129"/>
-      <c r="S43" s="130"/>
-      <c r="T43" s="128" t="s">
+      <c r="T45" s="131"/>
+      <c r="U45" s="132"/>
+      <c r="V45" s="130" t="s">
         <v>205</v>
       </c>
-      <c r="U43" s="129"/>
-      <c r="V43" s="130"/>
-      <c r="W43" s="128" t="s">
+      <c r="W45" s="131"/>
+      <c r="X45" s="132"/>
+      <c r="Y45" s="130" t="s">
         <v>206</v>
       </c>
-      <c r="X43" s="129"/>
-      <c r="Y43" s="130"/>
-      <c r="Z43" s="128" t="s">
+      <c r="Z45" s="131"/>
+      <c r="AA45" s="132"/>
+      <c r="AB45" s="130" t="s">
         <v>207</v>
       </c>
-      <c r="AA43" s="129"/>
-      <c r="AB43" s="130"/>
-      <c r="AC43" s="128" t="s">
+      <c r="AC45" s="131"/>
+      <c r="AD45" s="132"/>
+      <c r="AE45" s="130" t="s">
         <v>208</v>
       </c>
-      <c r="AD43" s="129"/>
-      <c r="AE43" s="130"/>
-      <c r="AF43" s="128" t="s">
+      <c r="AF45" s="131"/>
+      <c r="AG45" s="132"/>
+      <c r="AH45" s="130" t="s">
         <v>209</v>
       </c>
-      <c r="AG43" s="129"/>
-      <c r="AH43" s="130"/>
-      <c r="AI43" s="128" t="s">
+      <c r="AI45" s="131"/>
+      <c r="AJ45" s="132"/>
+      <c r="AK45" s="130" t="s">
         <v>210</v>
       </c>
-      <c r="AJ43" s="129"/>
-      <c r="AK43" s="130"/>
-      <c r="AL43" s="128" t="s">
+      <c r="AL45" s="131"/>
+      <c r="AM45" s="132"/>
+      <c r="AN45" s="130" t="s">
         <v>211</v>
       </c>
-      <c r="AM43" s="129"/>
-      <c r="AN43" s="130"/>
-      <c r="AO43" s="23"/>
-    </row>
-    <row r="44" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="19"/>
-      <c r="B44" s="122" t="s">
+      <c r="AO45" s="131"/>
+      <c r="AP45" s="132"/>
+      <c r="AQ45" s="23"/>
+    </row>
+    <row r="46" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C46" s="19"/>
+      <c r="D46" s="124" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="123"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="122" t="s">
+      <c r="E46" s="125"/>
+      <c r="F46" s="126"/>
+      <c r="G46" s="124" t="s">
         <v>141</v>
       </c>
-      <c r="F44" s="123"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="122" t="s">
+      <c r="H46" s="125"/>
+      <c r="I46" s="126"/>
+      <c r="J46" s="124" t="s">
         <v>142</v>
       </c>
-      <c r="I44" s="123"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="122" t="s">
+      <c r="K46" s="125"/>
+      <c r="L46" s="126"/>
+      <c r="M46" s="124" t="s">
         <v>143</v>
       </c>
-      <c r="L44" s="123"/>
-      <c r="M44" s="124"/>
-      <c r="N44" s="122" t="s">
+      <c r="N46" s="125"/>
+      <c r="O46" s="126"/>
+      <c r="P46" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="O44" s="123"/>
-      <c r="P44" s="124"/>
-      <c r="Q44" s="122" t="s">
+      <c r="Q46" s="125"/>
+      <c r="R46" s="126"/>
+      <c r="S46" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="R44" s="123"/>
-      <c r="S44" s="124"/>
-      <c r="T44" s="122" t="s">
+      <c r="T46" s="125"/>
+      <c r="U46" s="126"/>
+      <c r="V46" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="U44" s="123"/>
-      <c r="V44" s="124"/>
-      <c r="W44" s="122" t="s">
+      <c r="W46" s="125"/>
+      <c r="X46" s="126"/>
+      <c r="Y46" s="124" t="s">
         <v>147</v>
       </c>
-      <c r="X44" s="123"/>
-      <c r="Y44" s="124"/>
-      <c r="Z44" s="122" t="s">
+      <c r="Z46" s="125"/>
+      <c r="AA46" s="126"/>
+      <c r="AB46" s="124" t="s">
         <v>148</v>
       </c>
-      <c r="AA44" s="123"/>
-      <c r="AB44" s="124"/>
-      <c r="AC44" s="122" t="s">
+      <c r="AC46" s="125"/>
+      <c r="AD46" s="126"/>
+      <c r="AE46" s="124" t="s">
         <v>149</v>
       </c>
-      <c r="AD44" s="123"/>
-      <c r="AE44" s="124"/>
-      <c r="AF44" s="122" t="s">
+      <c r="AF46" s="125"/>
+      <c r="AG46" s="126"/>
+      <c r="AH46" s="124" t="s">
         <v>150</v>
       </c>
-      <c r="AG44" s="123"/>
-      <c r="AH44" s="124"/>
-      <c r="AI44" s="122" t="s">
+      <c r="AI46" s="125"/>
+      <c r="AJ46" s="126"/>
+      <c r="AK46" s="124" t="s">
         <v>151</v>
       </c>
-      <c r="AJ44" s="123"/>
-      <c r="AK44" s="124"/>
-      <c r="AL44" s="122" t="s">
+      <c r="AL46" s="125"/>
+      <c r="AM46" s="126"/>
+      <c r="AN46" s="124" t="s">
         <v>152</v>
       </c>
-      <c r="AM44" s="123"/>
-      <c r="AN44" s="124"/>
-      <c r="AO44" s="23"/>
-    </row>
-    <row r="45" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="19"/>
-      <c r="B45" s="125" t="s">
+      <c r="AO46" s="125"/>
+      <c r="AP46" s="126"/>
+      <c r="AQ46" s="23"/>
+    </row>
+    <row r="47" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C47" s="19"/>
+      <c r="D47" s="127" t="s">
         <v>212</v>
       </c>
-      <c r="C45" s="126"/>
-      <c r="D45" s="127"/>
-      <c r="E45" s="125" t="s">
+      <c r="E47" s="128"/>
+      <c r="F47" s="129"/>
+      <c r="G47" s="127" t="s">
         <v>213</v>
       </c>
-      <c r="F45" s="126"/>
-      <c r="G45" s="127"/>
-      <c r="H45" s="125" t="s">
+      <c r="H47" s="128"/>
+      <c r="I47" s="129"/>
+      <c r="J47" s="127" t="s">
         <v>214</v>
       </c>
-      <c r="I45" s="126"/>
-      <c r="J45" s="127"/>
-      <c r="K45" s="125" t="s">
+      <c r="K47" s="128"/>
+      <c r="L47" s="129"/>
+      <c r="M47" s="127" t="s">
         <v>215</v>
       </c>
-      <c r="L45" s="126"/>
-      <c r="M45" s="127"/>
-      <c r="N45" s="122" t="s">
+      <c r="N47" s="128"/>
+      <c r="O47" s="129"/>
+      <c r="P47" s="124" t="s">
         <v>166</v>
       </c>
-      <c r="O45" s="123"/>
-      <c r="P45" s="124"/>
-      <c r="Q45" s="122" t="s">
+      <c r="Q47" s="125"/>
+      <c r="R47" s="126"/>
+      <c r="S47" s="124" t="s">
         <v>167</v>
       </c>
-      <c r="R45" s="123"/>
-      <c r="S45" s="124"/>
-      <c r="T45" s="122" t="s">
+      <c r="T47" s="125"/>
+      <c r="U47" s="126"/>
+      <c r="V47" s="124" t="s">
         <v>168</v>
       </c>
-      <c r="U45" s="123"/>
-      <c r="V45" s="124"/>
-      <c r="W45" s="122" t="s">
+      <c r="W47" s="125"/>
+      <c r="X47" s="126"/>
+      <c r="Y47" s="124" t="s">
         <v>169</v>
       </c>
-      <c r="X45" s="123"/>
-      <c r="Y45" s="124"/>
-      <c r="Z45" s="122" t="s">
+      <c r="Z47" s="125"/>
+      <c r="AA47" s="126"/>
+      <c r="AB47" s="124" t="s">
         <v>170</v>
       </c>
-      <c r="AA45" s="123"/>
-      <c r="AB45" s="124"/>
-      <c r="AC45" s="122" t="s">
+      <c r="AC47" s="125"/>
+      <c r="AD47" s="126"/>
+      <c r="AE47" s="124" t="s">
         <v>171</v>
       </c>
-      <c r="AD45" s="123"/>
-      <c r="AE45" s="124"/>
-      <c r="AF45" s="122" t="s">
+      <c r="AF47" s="125"/>
+      <c r="AG47" s="126"/>
+      <c r="AH47" s="124" t="s">
         <v>172</v>
       </c>
-      <c r="AG45" s="123"/>
-      <c r="AH45" s="124"/>
-      <c r="AI45" s="122" t="s">
+      <c r="AI47" s="125"/>
+      <c r="AJ47" s="126"/>
+      <c r="AK47" s="124" t="s">
         <v>173</v>
       </c>
-      <c r="AJ45" s="123"/>
-      <c r="AK45" s="124"/>
-      <c r="AL45" s="122" t="s">
+      <c r="AL47" s="125"/>
+      <c r="AM47" s="126"/>
+      <c r="AN47" s="124" t="s">
         <v>174</v>
       </c>
-      <c r="AM45" s="123"/>
-      <c r="AN45" s="124"/>
-      <c r="AO45" s="23"/>
-      <c r="AQ45" s="125"/>
-      <c r="AR45" s="126"/>
-      <c r="AS45" s="127"/>
-      <c r="AT45" s="125"/>
-      <c r="AU45" s="126"/>
-      <c r="AV45" s="127"/>
-      <c r="AW45" s="125"/>
-      <c r="AX45" s="126"/>
-      <c r="AY45" s="127"/>
-      <c r="AZ45" s="125"/>
-      <c r="BA45" s="126"/>
-      <c r="BB45" s="127"/>
-      <c r="BC45" s="125"/>
-      <c r="BD45" s="126"/>
-      <c r="BE45" s="127"/>
-      <c r="BF45" s="125"/>
-      <c r="BG45" s="126"/>
-      <c r="BH45" s="127"/>
-      <c r="BI45" s="125"/>
-      <c r="BJ45" s="126"/>
-      <c r="BK45" s="127"/>
-      <c r="BL45" s="125"/>
-      <c r="BM45" s="126"/>
-      <c r="BN45" s="127"/>
-      <c r="BO45" s="125"/>
-      <c r="BP45" s="126"/>
-      <c r="BQ45" s="127"/>
-    </row>
-    <row r="46" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="20"/>
-      <c r="B46" s="122" t="s">
+      <c r="AO47" s="125"/>
+      <c r="AP47" s="126"/>
+      <c r="AQ47" s="23"/>
+      <c r="AS47" s="127"/>
+      <c r="AT47" s="128"/>
+      <c r="AU47" s="129"/>
+      <c r="AV47" s="127"/>
+      <c r="AW47" s="128"/>
+      <c r="AX47" s="129"/>
+      <c r="AY47" s="127"/>
+      <c r="AZ47" s="128"/>
+      <c r="BA47" s="129"/>
+      <c r="BB47" s="127"/>
+      <c r="BC47" s="128"/>
+      <c r="BD47" s="129"/>
+      <c r="BE47" s="127"/>
+      <c r="BF47" s="128"/>
+      <c r="BG47" s="129"/>
+      <c r="BH47" s="127"/>
+      <c r="BI47" s="128"/>
+      <c r="BJ47" s="129"/>
+      <c r="BK47" s="127"/>
+      <c r="BL47" s="128"/>
+      <c r="BM47" s="129"/>
+      <c r="BN47" s="127"/>
+      <c r="BO47" s="128"/>
+      <c r="BP47" s="129"/>
+      <c r="BQ47" s="127"/>
+      <c r="BR47" s="128"/>
+      <c r="BS47" s="129"/>
+    </row>
+    <row r="48" spans="3:71" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C48" s="20"/>
+      <c r="D48" s="124" t="s">
         <v>153</v>
       </c>
-      <c r="C46" s="123"/>
-      <c r="D46" s="124"/>
-      <c r="E46" s="122" t="s">
+      <c r="E48" s="125"/>
+      <c r="F48" s="126"/>
+      <c r="G48" s="124" t="s">
         <v>154</v>
       </c>
-      <c r="F46" s="123"/>
-      <c r="G46" s="124"/>
-      <c r="H46" s="122" t="s">
+      <c r="H48" s="125"/>
+      <c r="I48" s="126"/>
+      <c r="J48" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="I46" s="123"/>
-      <c r="J46" s="124"/>
-      <c r="K46" s="122" t="s">
+      <c r="K48" s="125"/>
+      <c r="L48" s="126"/>
+      <c r="M48" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="L46" s="123"/>
-      <c r="M46" s="124"/>
-      <c r="N46" s="125" t="s">
+      <c r="N48" s="125"/>
+      <c r="O48" s="126"/>
+      <c r="P48" s="127" t="s">
         <v>157</v>
       </c>
-      <c r="O46" s="126"/>
-      <c r="P46" s="127"/>
-      <c r="Q46" s="125" t="s">
+      <c r="Q48" s="128"/>
+      <c r="R48" s="129"/>
+      <c r="S48" s="127" t="s">
         <v>158</v>
       </c>
-      <c r="R46" s="126"/>
-      <c r="S46" s="127"/>
-      <c r="T46" s="125" t="s">
+      <c r="T48" s="128"/>
+      <c r="U48" s="129"/>
+      <c r="V48" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="U46" s="126"/>
-      <c r="V46" s="127"/>
-      <c r="W46" s="125" t="s">
+      <c r="W48" s="128"/>
+      <c r="X48" s="129"/>
+      <c r="Y48" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="X46" s="126"/>
-      <c r="Y46" s="127"/>
-      <c r="Z46" s="125" t="s">
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="129"/>
+      <c r="AB48" s="127" t="s">
         <v>161</v>
       </c>
-      <c r="AA46" s="126"/>
-      <c r="AB46" s="127"/>
-      <c r="AC46" s="125" t="s">
+      <c r="AC48" s="128"/>
+      <c r="AD48" s="129"/>
+      <c r="AE48" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="AD46" s="126"/>
-      <c r="AE46" s="127"/>
-      <c r="AF46" s="125" t="s">
+      <c r="AF48" s="128"/>
+      <c r="AG48" s="129"/>
+      <c r="AH48" s="127" t="s">
         <v>163</v>
       </c>
-      <c r="AG46" s="126"/>
-      <c r="AH46" s="127"/>
-      <c r="AI46" s="125" t="s">
+      <c r="AI48" s="128"/>
+      <c r="AJ48" s="129"/>
+      <c r="AK48" s="127" t="s">
         <v>164</v>
       </c>
-      <c r="AJ46" s="126"/>
-      <c r="AK46" s="127"/>
-      <c r="AL46" s="125" t="s">
+      <c r="AL48" s="128"/>
+      <c r="AM48" s="129"/>
+      <c r="AN48" s="127" t="s">
         <v>165</v>
       </c>
-      <c r="AM46" s="126"/>
-      <c r="AN46" s="127"/>
-      <c r="AO46" s="24"/>
-    </row>
-    <row r="47" spans="1:69" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="104" t="s">
+      <c r="AO48" s="128"/>
+      <c r="AP48" s="129"/>
+      <c r="AQ48" s="24"/>
+    </row>
+    <row r="49" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C49" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="105"/>
-      <c r="K47" s="105"/>
-      <c r="L47" s="105"/>
-      <c r="M47" s="105"/>
-      <c r="N47" s="105"/>
-      <c r="O47" s="105"/>
-      <c r="P47" s="105"/>
-      <c r="Q47" s="105"/>
-      <c r="R47" s="105"/>
-      <c r="S47" s="105"/>
-      <c r="T47" s="105"/>
-      <c r="U47" s="105"/>
-      <c r="V47" s="105"/>
-      <c r="W47" s="105" t="s">
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="105"/>
+      <c r="K49" s="105"/>
+      <c r="L49" s="105"/>
+      <c r="M49" s="105"/>
+      <c r="N49" s="105"/>
+      <c r="O49" s="105"/>
+      <c r="P49" s="105"/>
+      <c r="Q49" s="105"/>
+      <c r="R49" s="105"/>
+      <c r="S49" s="105"/>
+      <c r="T49" s="105"/>
+      <c r="U49" s="105"/>
+      <c r="V49" s="105"/>
+      <c r="W49" s="105"/>
+      <c r="X49" s="105"/>
+      <c r="Y49" s="105" t="s">
         <v>175</v>
       </c>
-      <c r="X47" s="105"/>
-      <c r="Y47" s="105"/>
-      <c r="Z47" s="105"/>
-      <c r="AA47" s="105"/>
-      <c r="AB47" s="3" t="s">
+      <c r="Z49" s="105"/>
+      <c r="AA49" s="105"/>
+      <c r="AB49" s="105"/>
+      <c r="AC49" s="105"/>
+      <c r="AD49" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3"/>
-      <c r="AG47" s="3"/>
-      <c r="AH47" s="3"/>
-      <c r="AI47" s="3"/>
-      <c r="AJ47" s="3"/>
-      <c r="AK47" s="3"/>
-      <c r="AL47" s="3"/>
-      <c r="AM47" s="3"/>
-      <c r="AN47" s="3"/>
-      <c r="AO47" s="17"/>
-    </row>
-    <row r="48" spans="1:69" ht="5.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="19"/>
-      <c r="AO48" s="23"/>
-    </row>
-    <row r="49" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="243" t="s">
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
+      <c r="AH49" s="3"/>
+      <c r="AI49" s="3"/>
+      <c r="AJ49" s="3"/>
+      <c r="AK49" s="3"/>
+      <c r="AL49" s="3"/>
+      <c r="AM49" s="3"/>
+      <c r="AN49" s="3"/>
+      <c r="AO49" s="3"/>
+      <c r="AP49" s="3"/>
+      <c r="AQ49" s="17"/>
+    </row>
+    <row r="50" spans="3:43" ht="5.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C50" s="19"/>
+      <c r="AQ50" s="23"/>
+    </row>
+    <row r="51" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C51" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="244"/>
-      <c r="C49" s="244"/>
-      <c r="D49" s="244"/>
-      <c r="E49" s="244"/>
-      <c r="F49" s="244"/>
-      <c r="G49" s="244"/>
-      <c r="H49" s="244"/>
-      <c r="I49" s="244"/>
-      <c r="J49" s="244"/>
-      <c r="K49" s="244"/>
-      <c r="L49" s="244"/>
-      <c r="M49" s="244"/>
-      <c r="N49" s="244"/>
-      <c r="O49" s="244"/>
-      <c r="P49" s="244"/>
-      <c r="Q49" s="244"/>
-      <c r="R49" s="244"/>
-      <c r="S49" s="244"/>
-      <c r="T49" s="244"/>
-      <c r="U49" s="244"/>
-      <c r="V49" s="119" t="s">
+      <c r="D51" s="120"/>
+      <c r="E51" s="120"/>
+      <c r="F51" s="120"/>
+      <c r="G51" s="120"/>
+      <c r="H51" s="120"/>
+      <c r="I51" s="120"/>
+      <c r="J51" s="120"/>
+      <c r="K51" s="120"/>
+      <c r="L51" s="120"/>
+      <c r="M51" s="120"/>
+      <c r="N51" s="120"/>
+      <c r="O51" s="120"/>
+      <c r="P51" s="120"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="120"/>
+      <c r="S51" s="120"/>
+      <c r="T51" s="120"/>
+      <c r="U51" s="120"/>
+      <c r="V51" s="120"/>
+      <c r="W51" s="120"/>
+      <c r="X51" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="W49" s="119"/>
-      <c r="X49" s="119"/>
-      <c r="Y49" s="119"/>
-      <c r="Z49" s="119" t="s">
+      <c r="Y51" s="121"/>
+      <c r="Z51" s="121"/>
+      <c r="AA51" s="121"/>
+      <c r="AB51" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="AA49" s="119"/>
-      <c r="AB49" s="119"/>
-      <c r="AC49" s="119"/>
-      <c r="AD49" s="120" t="s">
+      <c r="AC51" s="121"/>
+      <c r="AD51" s="121"/>
+      <c r="AE51" s="121"/>
+      <c r="AF51" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="AE49" s="109"/>
-      <c r="AF49" s="109"/>
-      <c r="AG49" s="109"/>
-      <c r="AH49" s="109"/>
-      <c r="AI49" s="109"/>
-      <c r="AJ49" s="109"/>
-      <c r="AK49" s="109"/>
-      <c r="AL49" s="109"/>
-      <c r="AM49" s="109"/>
-      <c r="AN49" s="109"/>
-      <c r="AO49" s="121"/>
-    </row>
-    <row r="50" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="104" t="s">
+      <c r="AG51" s="109"/>
+      <c r="AH51" s="109"/>
+      <c r="AI51" s="109"/>
+      <c r="AJ51" s="109"/>
+      <c r="AK51" s="109"/>
+      <c r="AL51" s="109"/>
+      <c r="AM51" s="109"/>
+      <c r="AN51" s="109"/>
+      <c r="AO51" s="109"/>
+      <c r="AP51" s="109"/>
+      <c r="AQ51" s="123"/>
+    </row>
+    <row r="52" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C52" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="105"/>
-      <c r="I50" s="105"/>
-      <c r="J50" s="105"/>
-      <c r="K50" s="105"/>
-      <c r="L50" s="105"/>
-      <c r="M50" s="105"/>
-      <c r="N50" s="105"/>
-      <c r="O50" s="105"/>
-      <c r="P50" s="105"/>
-      <c r="Q50" s="105"/>
-      <c r="R50" s="105"/>
-      <c r="S50" s="105"/>
-      <c r="T50" s="105"/>
-      <c r="U50" s="106"/>
-      <c r="V50" s="118" t="s">
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="105"/>
+      <c r="K52" s="105"/>
+      <c r="L52" s="105"/>
+      <c r="M52" s="105"/>
+      <c r="N52" s="105"/>
+      <c r="O52" s="105"/>
+      <c r="P52" s="105"/>
+      <c r="Q52" s="105"/>
+      <c r="R52" s="105"/>
+      <c r="S52" s="105"/>
+      <c r="T52" s="105"/>
+      <c r="U52" s="105"/>
+      <c r="V52" s="105"/>
+      <c r="W52" s="106"/>
+      <c r="X52" s="118" t="s">
         <v>176</v>
       </c>
-      <c r="W50" s="118"/>
-      <c r="X50" s="118"/>
-      <c r="Y50" s="118"/>
-      <c r="Z50" s="118" t="s">
+      <c r="Y52" s="118"/>
+      <c r="Z52" s="118"/>
+      <c r="AA52" s="118"/>
+      <c r="AB52" s="118" t="s">
         <v>177</v>
       </c>
-      <c r="AA50" s="118"/>
-      <c r="AB50" s="118"/>
-      <c r="AC50" s="118"/>
-      <c r="AD50" s="2"/>
-      <c r="AE50" s="3"/>
-      <c r="AF50" s="43" t="s">
+      <c r="AC52" s="118"/>
+      <c r="AD52" s="118"/>
+      <c r="AE52" s="118"/>
+      <c r="AF52" s="2"/>
+      <c r="AG52" s="3"/>
+      <c r="AH52" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="AG50" s="39" t="s">
+      <c r="AI52" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH50" s="40"/>
-      <c r="AI50" s="41"/>
-      <c r="AJ50" s="42"/>
-      <c r="AK50" s="43" t="s">
+      <c r="AJ52" s="40"/>
+      <c r="AK52" s="41"/>
+      <c r="AL52" s="42"/>
+      <c r="AM52" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="AL50" s="39" t="s">
+      <c r="AN52" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM50" s="40"/>
-      <c r="AN50" s="40"/>
-      <c r="AO50" s="17"/>
-    </row>
-    <row r="51" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="67"/>
-      <c r="B51" s="109" t="s">
+      <c r="AO52" s="40"/>
+      <c r="AP52" s="40"/>
+      <c r="AQ52" s="17"/>
+    </row>
+    <row r="53" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C53" s="67"/>
+      <c r="D53" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="109"/>
-      <c r="D51" s="109"/>
-      <c r="E51" s="109"/>
-      <c r="F51" s="109"/>
-      <c r="G51" s="109"/>
-      <c r="H51" s="109"/>
-      <c r="I51" s="109"/>
-      <c r="J51" s="109"/>
-      <c r="K51" s="109"/>
-      <c r="L51" s="109"/>
-      <c r="M51" s="69" t="s">
+      <c r="E53" s="109"/>
+      <c r="F53" s="109"/>
+      <c r="G53" s="109"/>
+      <c r="H53" s="109"/>
+      <c r="I53" s="109"/>
+      <c r="J53" s="109"/>
+      <c r="K53" s="109"/>
+      <c r="L53" s="109"/>
+      <c r="M53" s="109"/>
+      <c r="N53" s="109"/>
+      <c r="O53" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="N51" s="69" t="s">
+      <c r="P53" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="O51" s="69" t="s">
+      <c r="Q53" s="69" t="s">
         <v>182</v>
       </c>
-      <c r="P51" s="69" t="s">
+      <c r="R53" s="69" t="s">
         <v>183</v>
       </c>
-      <c r="Q51" s="69" t="s">
+      <c r="S53" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="R51" s="69" t="s">
+      <c r="T53" s="69" t="s">
         <v>185</v>
       </c>
-      <c r="S51" s="69" t="s">
+      <c r="U53" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="T51" s="69" t="s">
+      <c r="V53" s="69" t="s">
         <v>187</v>
       </c>
-      <c r="U51" s="69" t="s">
+      <c r="W53" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="V51" s="69" t="s">
+      <c r="X53" s="69" t="s">
         <v>189</v>
       </c>
-      <c r="W51" s="69" t="s">
+      <c r="Y53" s="69" t="s">
         <v>190</v>
       </c>
-      <c r="X51" s="69" t="s">
+      <c r="Z53" s="69" t="s">
         <v>191</v>
       </c>
-      <c r="Y51" s="69"/>
-      <c r="Z51" s="69"/>
-      <c r="AA51" s="69"/>
-      <c r="AB51" s="69"/>
-      <c r="AC51" s="69"/>
-      <c r="AD51" s="69"/>
-      <c r="AE51" s="69"/>
-      <c r="AF51" s="69"/>
-      <c r="AG51" s="69"/>
-      <c r="AH51" s="69"/>
-      <c r="AI51" s="69"/>
-      <c r="AJ51" s="69"/>
-      <c r="AK51" s="69"/>
-      <c r="AL51" s="69"/>
-      <c r="AM51" s="69"/>
-      <c r="AN51" s="69"/>
-      <c r="AO51" s="28" t="e">
+      <c r="AA53" s="69"/>
+      <c r="AB53" s="69"/>
+      <c r="AC53" s="69"/>
+      <c r="AD53" s="69"/>
+      <c r="AE53" s="69"/>
+      <c r="AF53" s="69"/>
+      <c r="AG53" s="69"/>
+      <c r="AH53" s="69"/>
+      <c r="AI53" s="69"/>
+      <c r="AJ53" s="69"/>
+      <c r="AK53" s="69"/>
+      <c r="AL53" s="69"/>
+      <c r="AM53" s="69"/>
+      <c r="AN53" s="69"/>
+      <c r="AO53" s="69"/>
+      <c r="AP53" s="69"/>
+      <c r="AQ53" s="28" t="e">
         <f>IF(#REF!=1,#REF!,0)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="52" spans="1:41" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="19"/>
-      <c r="AO52" s="23"/>
-    </row>
-    <row r="53" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="104" t="s">
+    <row r="54" spans="3:43" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C54" s="19"/>
+      <c r="AQ54" s="23"/>
+    </row>
+    <row r="55" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C55" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="105"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="105"/>
-      <c r="E53" s="105"/>
-      <c r="F53" s="105"/>
-      <c r="G53" s="105"/>
-      <c r="H53" s="105"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="105"/>
-      <c r="K53" s="105"/>
-      <c r="L53" s="105"/>
-      <c r="M53" s="105"/>
-      <c r="N53" s="105"/>
-      <c r="O53" s="105"/>
-      <c r="P53" s="105"/>
-      <c r="Q53" s="105"/>
-      <c r="R53" s="105"/>
-      <c r="S53" s="105"/>
-      <c r="T53" s="105"/>
-      <c r="U53" s="106"/>
-      <c r="V53" s="118" t="s">
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="105"/>
+      <c r="K55" s="105"/>
+      <c r="L55" s="105"/>
+      <c r="M55" s="105"/>
+      <c r="N55" s="105"/>
+      <c r="O55" s="105"/>
+      <c r="P55" s="105"/>
+      <c r="Q55" s="105"/>
+      <c r="R55" s="105"/>
+      <c r="S55" s="105"/>
+      <c r="T55" s="105"/>
+      <c r="U55" s="105"/>
+      <c r="V55" s="105"/>
+      <c r="W55" s="106"/>
+      <c r="X55" s="118" t="s">
         <v>195</v>
       </c>
-      <c r="W53" s="118"/>
-      <c r="X53" s="118"/>
-      <c r="Y53" s="118"/>
-      <c r="Z53" s="118" t="s">
+      <c r="Y55" s="118"/>
+      <c r="Z55" s="118"/>
+      <c r="AA55" s="118"/>
+      <c r="AB55" s="118" t="s">
         <v>192</v>
       </c>
-      <c r="AA53" s="118"/>
-      <c r="AB53" s="118"/>
-      <c r="AC53" s="118"/>
-      <c r="AD53" s="2"/>
-      <c r="AE53" s="3"/>
-      <c r="AF53" s="43" t="s">
+      <c r="AC55" s="118"/>
+      <c r="AD55" s="118"/>
+      <c r="AE55" s="118"/>
+      <c r="AF55" s="2"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="AG53" s="39" t="s">
+      <c r="AI55" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH53" s="40"/>
-      <c r="AI53" s="41"/>
-      <c r="AJ53" s="42"/>
-      <c r="AK53" s="43" t="s">
+      <c r="AJ55" s="40"/>
+      <c r="AK55" s="41"/>
+      <c r="AL55" s="42"/>
+      <c r="AM55" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="AL53" s="39" t="s">
+      <c r="AN55" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM53" s="40"/>
-      <c r="AN53" s="40"/>
-      <c r="AO53" s="17"/>
-    </row>
-    <row r="54" spans="1:41" ht="4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="71"/>
-      <c r="B54" s="70"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="70"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="70"/>
-      <c r="M54" s="70"/>
-      <c r="N54" s="70"/>
-      <c r="O54" s="70"/>
-      <c r="P54" s="70"/>
-      <c r="Q54" s="70"/>
-      <c r="R54" s="70"/>
-      <c r="S54" s="70"/>
-      <c r="T54" s="70"/>
-      <c r="U54" s="70"/>
-      <c r="V54" s="58"/>
-      <c r="W54" s="58"/>
-      <c r="X54" s="58"/>
-      <c r="Y54" s="58"/>
-      <c r="Z54" s="58"/>
-      <c r="AA54" s="58"/>
-      <c r="AB54" s="58"/>
-      <c r="AC54" s="58"/>
-      <c r="AF54" s="59"/>
-      <c r="AG54" s="60"/>
-      <c r="AH54" s="61"/>
-      <c r="AI54" s="62"/>
-      <c r="AJ54" s="63"/>
-      <c r="AK54" s="59"/>
-      <c r="AL54" s="60"/>
-      <c r="AM54" s="61"/>
-      <c r="AN54" s="61"/>
-      <c r="AO54" s="23"/>
-    </row>
-    <row r="55" spans="1:41" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="110" t="s">
+      <c r="AO55" s="40"/>
+      <c r="AP55" s="40"/>
+      <c r="AQ55" s="17"/>
+    </row>
+    <row r="56" spans="3:43" ht="4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C56" s="71"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="70"/>
+      <c r="M56" s="70"/>
+      <c r="N56" s="70"/>
+      <c r="O56" s="70"/>
+      <c r="P56" s="70"/>
+      <c r="Q56" s="70"/>
+      <c r="R56" s="70"/>
+      <c r="S56" s="70"/>
+      <c r="T56" s="70"/>
+      <c r="U56" s="70"/>
+      <c r="V56" s="70"/>
+      <c r="W56" s="70"/>
+      <c r="X56" s="58"/>
+      <c r="Y56" s="58"/>
+      <c r="Z56" s="58"/>
+      <c r="AA56" s="58"/>
+      <c r="AB56" s="58"/>
+      <c r="AC56" s="58"/>
+      <c r="AD56" s="58"/>
+      <c r="AE56" s="58"/>
+      <c r="AH56" s="59"/>
+      <c r="AI56" s="60"/>
+      <c r="AJ56" s="61"/>
+      <c r="AK56" s="62"/>
+      <c r="AL56" s="63"/>
+      <c r="AM56" s="59"/>
+      <c r="AN56" s="60"/>
+      <c r="AO56" s="61"/>
+      <c r="AP56" s="61"/>
+      <c r="AQ56" s="23"/>
+    </row>
+    <row r="57" spans="3:43" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C57" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="111"/>
-      <c r="C55" s="111"/>
-      <c r="D55" s="111"/>
-      <c r="E55" s="111"/>
-      <c r="F55" s="111"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111"/>
-      <c r="I55" s="111"/>
-      <c r="J55" s="111"/>
-      <c r="K55" s="111"/>
-      <c r="L55" s="111"/>
-      <c r="M55" s="111"/>
-      <c r="N55" s="111"/>
-      <c r="O55" s="111"/>
-      <c r="P55" s="111"/>
-      <c r="Q55" s="111"/>
-      <c r="R55" s="111"/>
-      <c r="S55" s="111"/>
-      <c r="T55" s="111"/>
-      <c r="U55" s="111"/>
-      <c r="V55" s="111"/>
-      <c r="W55" s="111"/>
-      <c r="X55" s="111"/>
-      <c r="Y55" s="111"/>
-      <c r="Z55" s="112" t="s">
+      <c r="D57" s="111"/>
+      <c r="E57" s="111"/>
+      <c r="F57" s="111"/>
+      <c r="G57" s="111"/>
+      <c r="H57" s="111"/>
+      <c r="I57" s="111"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="111"/>
+      <c r="M57" s="111"/>
+      <c r="N57" s="111"/>
+      <c r="O57" s="111"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="111"/>
+      <c r="S57" s="111"/>
+      <c r="T57" s="111"/>
+      <c r="U57" s="111"/>
+      <c r="V57" s="111"/>
+      <c r="W57" s="111"/>
+      <c r="X57" s="111"/>
+      <c r="Y57" s="111"/>
+      <c r="Z57" s="111"/>
+      <c r="AA57" s="111"/>
+      <c r="AB57" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="AA55" s="112"/>
-      <c r="AB55" s="112"/>
-      <c r="AC55" s="112"/>
-      <c r="AD55" s="112"/>
-      <c r="AE55" s="112"/>
-      <c r="AF55" s="112"/>
-      <c r="AG55" s="112"/>
-      <c r="AH55" s="112"/>
-      <c r="AI55" s="112"/>
-      <c r="AJ55" s="112"/>
-      <c r="AK55" s="112"/>
-      <c r="AL55" s="112"/>
-      <c r="AM55" s="112"/>
-      <c r="AN55" s="112"/>
-      <c r="AO55" s="113"/>
-    </row>
-    <row r="56" spans="1:41" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="57" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A57" s="76" t="s">
+      <c r="AC57" s="112"/>
+      <c r="AD57" s="112"/>
+      <c r="AE57" s="112"/>
+      <c r="AF57" s="112"/>
+      <c r="AG57" s="112"/>
+      <c r="AH57" s="112"/>
+      <c r="AI57" s="112"/>
+      <c r="AJ57" s="112"/>
+      <c r="AK57" s="112"/>
+      <c r="AL57" s="112"/>
+      <c r="AM57" s="112"/>
+      <c r="AN57" s="112"/>
+      <c r="AO57" s="112"/>
+      <c r="AP57" s="112"/>
+      <c r="AQ57" s="113"/>
+    </row>
+    <row r="58" spans="3:43" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="59" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C59" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="77"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="77"/>
-      <c r="K57" s="77"/>
-      <c r="L57" s="77"/>
-      <c r="M57" s="114" t="s">
+      <c r="D59" s="77"/>
+      <c r="E59" s="77"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="77"/>
+      <c r="I59" s="77"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="77"/>
+      <c r="L59" s="77"/>
+      <c r="M59" s="77"/>
+      <c r="N59" s="77"/>
+      <c r="O59" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="N57" s="115"/>
-      <c r="O57" s="115"/>
-      <c r="P57" s="115"/>
-      <c r="Q57" s="115"/>
-      <c r="R57" s="115"/>
-      <c r="S57" s="115"/>
-      <c r="T57" s="115"/>
-      <c r="U57" s="56" t="s">
+      <c r="P59" s="115"/>
+      <c r="Q59" s="115"/>
+      <c r="R59" s="115"/>
+      <c r="S59" s="115"/>
+      <c r="T59" s="115"/>
+      <c r="U59" s="115"/>
+      <c r="V59" s="115"/>
+      <c r="W59" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="V57" s="57"/>
-      <c r="W57" s="57"/>
-      <c r="X57" s="116" t="s">
+      <c r="X59" s="57"/>
+      <c r="Y59" s="57"/>
+      <c r="Z59" s="116" t="s">
         <v>197</v>
       </c>
-      <c r="Y57" s="116"/>
-      <c r="Z57" s="116"/>
-      <c r="AA57" s="116"/>
-      <c r="AB57" s="116"/>
-      <c r="AC57" s="117"/>
-      <c r="AD57" s="79" t="s">
+      <c r="AA59" s="116"/>
+      <c r="AB59" s="116"/>
+      <c r="AC59" s="116"/>
+      <c r="AD59" s="116"/>
+      <c r="AE59" s="117"/>
+      <c r="AF59" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AE57" s="80"/>
-      <c r="AF57" s="80"/>
-      <c r="AG57" s="80"/>
-      <c r="AH57" s="80"/>
-      <c r="AI57" s="80"/>
-      <c r="AJ57" s="80"/>
-      <c r="AK57" s="80"/>
-      <c r="AL57" s="80"/>
-      <c r="AM57" s="80"/>
-      <c r="AN57" s="80"/>
-      <c r="AO57" s="81"/>
-    </row>
-    <row r="58" spans="1:41" ht="15" x14ac:dyDescent="0.4">
-      <c r="A58" s="51"/>
-      <c r="B58" s="29" t="s">
+      <c r="AG59" s="80"/>
+      <c r="AH59" s="80"/>
+      <c r="AI59" s="80"/>
+      <c r="AJ59" s="80"/>
+      <c r="AK59" s="80"/>
+      <c r="AL59" s="80"/>
+      <c r="AM59" s="80"/>
+      <c r="AN59" s="80"/>
+      <c r="AO59" s="80"/>
+      <c r="AP59" s="80"/>
+      <c r="AQ59" s="81"/>
+    </row>
+    <row r="60" spans="3:43" ht="15" x14ac:dyDescent="0.4">
+      <c r="C60" s="51"/>
+      <c r="D60" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
-      <c r="M58" s="52"/>
-      <c r="N58" s="52"/>
-      <c r="O58" s="52"/>
-      <c r="P58" s="52"/>
-      <c r="Q58" s="52"/>
-      <c r="R58" s="52"/>
-      <c r="S58" s="52"/>
-      <c r="T58" s="52"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="52"/>
-      <c r="W58" s="52"/>
-      <c r="X58" s="52"/>
-      <c r="Y58" s="52"/>
-      <c r="Z58" s="52"/>
-      <c r="AA58" s="52"/>
-      <c r="AB58" s="52"/>
-      <c r="AC58" s="53"/>
-      <c r="AD58" s="68"/>
-      <c r="AE58" s="3"/>
-      <c r="AF58" s="43" t="s">
+      <c r="E60" s="52"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52"/>
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
+      <c r="P60" s="52"/>
+      <c r="Q60" s="52"/>
+      <c r="R60" s="52"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="52"/>
+      <c r="U60" s="52"/>
+      <c r="V60" s="52"/>
+      <c r="W60" s="52"/>
+      <c r="X60" s="52"/>
+      <c r="Y60" s="52"/>
+      <c r="Z60" s="52"/>
+      <c r="AA60" s="52"/>
+      <c r="AB60" s="52"/>
+      <c r="AC60" s="52"/>
+      <c r="AD60" s="52"/>
+      <c r="AE60" s="53"/>
+      <c r="AF60" s="68"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG58" s="39" t="s">
+      <c r="AI60" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH58" s="40"/>
-      <c r="AI58" s="41"/>
-      <c r="AJ58" s="42"/>
-      <c r="AK58" s="43"/>
-      <c r="AL58" s="39" t="s">
+      <c r="AJ60" s="40"/>
+      <c r="AK60" s="41"/>
+      <c r="AL60" s="42"/>
+      <c r="AM60" s="43"/>
+      <c r="AN60" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM58" s="40"/>
-      <c r="AN58" s="40"/>
-      <c r="AO58" s="17"/>
-    </row>
-    <row r="59" spans="1:41" ht="15" x14ac:dyDescent="0.4">
-      <c r="A59" s="33"/>
-      <c r="B59" s="29" t="s">
+      <c r="AO60" s="40"/>
+      <c r="AP60" s="40"/>
+      <c r="AQ60" s="17"/>
+    </row>
+    <row r="61" spans="3:43" ht="15" x14ac:dyDescent="0.4">
+      <c r="C61" s="33"/>
+      <c r="D61" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C59" s="30"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
-      <c r="AB59" s="3"/>
-      <c r="AC59" s="4"/>
-      <c r="AD59" s="2"/>
-      <c r="AE59" s="3"/>
-      <c r="AF59" s="43" t="s">
+      <c r="E61" s="30"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="4"/>
+      <c r="AF61" s="2"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG59" s="39" t="s">
+      <c r="AI61" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH59" s="40"/>
-      <c r="AI59" s="41"/>
-      <c r="AJ59" s="42"/>
-      <c r="AK59" s="43"/>
-      <c r="AL59" s="39" t="s">
+      <c r="AJ61" s="40"/>
+      <c r="AK61" s="41"/>
+      <c r="AL61" s="42"/>
+      <c r="AM61" s="43"/>
+      <c r="AN61" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM59" s="40"/>
-      <c r="AN59" s="40"/>
-      <c r="AO59" s="17"/>
-    </row>
-    <row r="60" spans="1:41" ht="15.45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="46"/>
-      <c r="B60" s="47" t="s">
+      <c r="AO61" s="40"/>
+      <c r="AP61" s="40"/>
+      <c r="AQ61" s="17"/>
+    </row>
+    <row r="62" spans="3:43" ht="15.45" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C62" s="46"/>
+      <c r="D62" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="C60" s="48"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
-      <c r="L60" s="48"/>
-      <c r="M60" s="26"/>
-      <c r="N60" s="26"/>
-      <c r="O60" s="26"/>
-      <c r="P60" s="26"/>
-      <c r="Q60" s="26"/>
-      <c r="R60" s="26"/>
-      <c r="S60" s="26"/>
-      <c r="T60" s="26"/>
-      <c r="U60" s="26"/>
-      <c r="V60" s="26"/>
-      <c r="W60" s="26"/>
-      <c r="X60" s="26"/>
-      <c r="Y60" s="26"/>
-      <c r="Z60" s="26"/>
-      <c r="AA60" s="26"/>
-      <c r="AB60" s="26"/>
-      <c r="AC60" s="50"/>
-      <c r="AD60" s="25"/>
-      <c r="AE60" s="26"/>
-      <c r="AF60" s="45" t="s">
+      <c r="E62" s="48"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="48"/>
+      <c r="M62" s="48"/>
+      <c r="N62" s="48"/>
+      <c r="O62" s="26"/>
+      <c r="P62" s="26"/>
+      <c r="Q62" s="26"/>
+      <c r="R62" s="26"/>
+      <c r="S62" s="26"/>
+      <c r="T62" s="26"/>
+      <c r="U62" s="26"/>
+      <c r="V62" s="26"/>
+      <c r="W62" s="26"/>
+      <c r="X62" s="26"/>
+      <c r="Y62" s="26"/>
+      <c r="Z62" s="26"/>
+      <c r="AA62" s="26"/>
+      <c r="AB62" s="26"/>
+      <c r="AC62" s="26"/>
+      <c r="AD62" s="26"/>
+      <c r="AE62" s="50"/>
+      <c r="AF62" s="25"/>
+      <c r="AG62" s="26"/>
+      <c r="AH62" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="AG60" s="35" t="s">
+      <c r="AI62" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="AH60" s="36"/>
-      <c r="AI60" s="37"/>
-      <c r="AJ60" s="38"/>
-      <c r="AK60" s="45"/>
-      <c r="AL60" s="35" t="s">
+      <c r="AJ62" s="36"/>
+      <c r="AK62" s="37"/>
+      <c r="AL62" s="38"/>
+      <c r="AM62" s="45"/>
+      <c r="AN62" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="AM60" s="36"/>
-      <c r="AN60" s="36"/>
-      <c r="AO60" s="27"/>
-    </row>
-    <row r="61" spans="1:41" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="62" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="76" t="s">
+      <c r="AO62" s="36"/>
+      <c r="AP62" s="36"/>
+      <c r="AQ62" s="27"/>
+    </row>
+    <row r="63" spans="3:43" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="64" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C64" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="77"/>
-      <c r="C62" s="77"/>
-      <c r="D62" s="77"/>
-      <c r="E62" s="77"/>
-      <c r="F62" s="77"/>
-      <c r="G62" s="77"/>
-      <c r="H62" s="77"/>
-      <c r="I62" s="77"/>
-      <c r="J62" s="77"/>
-      <c r="K62" s="77"/>
-      <c r="L62" s="77"/>
-      <c r="M62" s="77"/>
-      <c r="N62" s="77"/>
-      <c r="O62" s="77"/>
-      <c r="P62" s="77"/>
-      <c r="Q62" s="77"/>
-      <c r="R62" s="77"/>
-      <c r="S62" s="77"/>
-      <c r="T62" s="77"/>
-      <c r="U62" s="77"/>
-      <c r="V62" s="77"/>
-      <c r="W62" s="77"/>
-      <c r="X62" s="77"/>
-      <c r="Y62" s="77"/>
-      <c r="Z62" s="77"/>
-      <c r="AA62" s="77"/>
-      <c r="AB62" s="77"/>
-      <c r="AC62" s="78"/>
-      <c r="AD62" s="79" t="s">
+      <c r="D64" s="77"/>
+      <c r="E64" s="77"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="77"/>
+      <c r="I64" s="77"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="77"/>
+      <c r="L64" s="77"/>
+      <c r="M64" s="77"/>
+      <c r="N64" s="77"/>
+      <c r="O64" s="77"/>
+      <c r="P64" s="77"/>
+      <c r="Q64" s="77"/>
+      <c r="R64" s="77"/>
+      <c r="S64" s="77"/>
+      <c r="T64" s="77"/>
+      <c r="U64" s="77"/>
+      <c r="V64" s="77"/>
+      <c r="W64" s="77"/>
+      <c r="X64" s="77"/>
+      <c r="Y64" s="77"/>
+      <c r="Z64" s="77"/>
+      <c r="AA64" s="77"/>
+      <c r="AB64" s="77"/>
+      <c r="AC64" s="77"/>
+      <c r="AD64" s="77"/>
+      <c r="AE64" s="78"/>
+      <c r="AF64" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="AE62" s="80"/>
-      <c r="AF62" s="80"/>
-      <c r="AG62" s="80"/>
-      <c r="AH62" s="80"/>
-      <c r="AI62" s="80"/>
-      <c r="AJ62" s="80"/>
-      <c r="AK62" s="80"/>
-      <c r="AL62" s="80"/>
-      <c r="AM62" s="80"/>
-      <c r="AN62" s="80"/>
-      <c r="AO62" s="81"/>
-    </row>
-    <row r="63" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="33"/>
-      <c r="B63" s="29" t="s">
+      <c r="AG64" s="80"/>
+      <c r="AH64" s="80"/>
+      <c r="AI64" s="80"/>
+      <c r="AJ64" s="80"/>
+      <c r="AK64" s="80"/>
+      <c r="AL64" s="80"/>
+      <c r="AM64" s="80"/>
+      <c r="AN64" s="80"/>
+      <c r="AO64" s="80"/>
+      <c r="AP64" s="80"/>
+      <c r="AQ64" s="81"/>
+    </row>
+    <row r="65" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C65" s="33"/>
+      <c r="D65" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="30"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="30"/>
-      <c r="K63" s="30"/>
-      <c r="L63" s="30"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
-      <c r="AB63" s="3"/>
-      <c r="AC63" s="4"/>
-      <c r="AD63" s="2"/>
-      <c r="AE63" s="3"/>
-      <c r="AF63" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG63" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH63" s="40"/>
-      <c r="AI63" s="41"/>
-      <c r="AJ63" s="42"/>
-      <c r="AK63" s="43"/>
-      <c r="AL63" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM63" s="40"/>
-      <c r="AN63" s="40"/>
-      <c r="AO63" s="17"/>
-    </row>
-    <row r="64" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="33"/>
-      <c r="B64" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="30"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
-      <c r="AB64" s="3"/>
-      <c r="AC64" s="4"/>
-      <c r="AD64" s="2"/>
-      <c r="AE64" s="3"/>
-      <c r="AF64" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG64" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH64" s="40"/>
-      <c r="AI64" s="41"/>
-      <c r="AJ64" s="42"/>
-      <c r="AK64" s="43"/>
-      <c r="AL64" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM64" s="40"/>
-      <c r="AN64" s="40"/>
-      <c r="AO64" s="17"/>
-    </row>
-    <row r="65" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="33"/>
-      <c r="B65" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="30"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
+      <c r="E65" s="30"/>
       <c r="F65" s="31"/>
       <c r="G65" s="31"/>
       <c r="H65" s="31"/>
       <c r="I65" s="31"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
+      <c r="J65" s="31"/>
+      <c r="K65" s="31"/>
       <c r="L65" s="30"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
+      <c r="M65" s="30"/>
+      <c r="N65" s="30"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
@@ -5413,43 +5308,43 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
-      <c r="AC65" s="4"/>
-      <c r="AD65" s="2"/>
-      <c r="AE65" s="3"/>
-      <c r="AF65" s="43" t="s">
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="2"/>
+      <c r="AG65" s="3"/>
+      <c r="AH65" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG65" s="39" t="s">
+      <c r="AI65" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH65" s="40"/>
-      <c r="AI65" s="41"/>
-      <c r="AJ65" s="42"/>
-      <c r="AK65" s="43"/>
-      <c r="AL65" s="39" t="s">
+      <c r="AJ65" s="40"/>
+      <c r="AK65" s="41"/>
+      <c r="AL65" s="42"/>
+      <c r="AM65" s="43"/>
+      <c r="AN65" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM65" s="40"/>
-      <c r="AN65" s="40"/>
-      <c r="AO65" s="17"/>
-    </row>
-    <row r="66" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="33"/>
-      <c r="B66" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C66" s="30"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
+      <c r="AO65" s="40"/>
+      <c r="AP65" s="40"/>
+      <c r="AQ65" s="17"/>
+    </row>
+    <row r="66" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C66" s="33"/>
+      <c r="D66" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" s="30"/>
       <c r="F66" s="31"/>
       <c r="G66" s="31"/>
       <c r="H66" s="31"/>
       <c r="I66" s="31"/>
-      <c r="J66" s="30"/>
-      <c r="K66" s="30"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="31"/>
       <c r="L66" s="30"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="30"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
@@ -5464,208 +5359,212 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
-      <c r="AC66" s="4"/>
-      <c r="AD66" s="2"/>
-      <c r="AE66" s="3"/>
-      <c r="AF66" s="43" t="s">
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="2"/>
+      <c r="AG66" s="3"/>
+      <c r="AH66" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG66" s="39" t="s">
+      <c r="AI66" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AH66" s="40"/>
-      <c r="AI66" s="41"/>
-      <c r="AJ66" s="42"/>
-      <c r="AK66" s="43"/>
-      <c r="AL66" s="39" t="s">
+      <c r="AJ66" s="40"/>
+      <c r="AK66" s="41"/>
+      <c r="AL66" s="42"/>
+      <c r="AM66" s="43"/>
+      <c r="AN66" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AM66" s="40"/>
-      <c r="AN66" s="40"/>
-      <c r="AO66" s="17"/>
-    </row>
-    <row r="67" spans="1:41" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="19"/>
-      <c r="AO67" s="23"/>
-    </row>
-    <row r="68" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="104" t="s">
+      <c r="AO66" s="40"/>
+      <c r="AP66" s="40"/>
+      <c r="AQ66" s="17"/>
+    </row>
+    <row r="67" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C67" s="33"/>
+      <c r="D67" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="30"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="2"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI67" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ67" s="40"/>
+      <c r="AK67" s="41"/>
+      <c r="AL67" s="42"/>
+      <c r="AM67" s="43"/>
+      <c r="AN67" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO67" s="40"/>
+      <c r="AP67" s="40"/>
+      <c r="AQ67" s="17"/>
+    </row>
+    <row r="68" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C68" s="33"/>
+      <c r="D68" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="30"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="31"/>
+      <c r="J68" s="31"/>
+      <c r="K68" s="31"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="30"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="4"/>
+      <c r="AF68" s="2"/>
+      <c r="AG68" s="3"/>
+      <c r="AH68" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI68" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ68" s="40"/>
+      <c r="AK68" s="41"/>
+      <c r="AL68" s="42"/>
+      <c r="AM68" s="43"/>
+      <c r="AN68" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO68" s="40"/>
+      <c r="AP68" s="40"/>
+      <c r="AQ68" s="17"/>
+    </row>
+    <row r="69" spans="3:43" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C69" s="19"/>
+      <c r="AQ69" s="23"/>
+    </row>
+    <row r="70" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C70" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="105"/>
-      <c r="C68" s="105"/>
-      <c r="D68" s="105"/>
-      <c r="E68" s="105"/>
-      <c r="F68" s="105"/>
-      <c r="G68" s="105"/>
-      <c r="H68" s="105"/>
-      <c r="I68" s="105"/>
-      <c r="J68" s="106"/>
-      <c r="K68" s="107" t="s">
+      <c r="D70" s="105"/>
+      <c r="E70" s="105"/>
+      <c r="F70" s="105"/>
+      <c r="G70" s="105"/>
+      <c r="H70" s="105"/>
+      <c r="I70" s="105"/>
+      <c r="J70" s="105"/>
+      <c r="K70" s="105"/>
+      <c r="L70" s="106"/>
+      <c r="M70" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="L68" s="105"/>
-      <c r="M68" s="105"/>
-      <c r="N68" s="105"/>
-      <c r="O68" s="105"/>
-      <c r="P68" s="105"/>
-      <c r="Q68" s="105"/>
-      <c r="R68" s="105"/>
-      <c r="S68" s="105"/>
-      <c r="T68" s="105"/>
-      <c r="U68" s="105"/>
-      <c r="V68" s="105"/>
-      <c r="W68" s="105" t="s">
+      <c r="N70" s="105"/>
+      <c r="O70" s="105"/>
+      <c r="P70" s="105"/>
+      <c r="Q70" s="105"/>
+      <c r="R70" s="105"/>
+      <c r="S70" s="105"/>
+      <c r="T70" s="105"/>
+      <c r="U70" s="105"/>
+      <c r="V70" s="105"/>
+      <c r="W70" s="105"/>
+      <c r="X70" s="105"/>
+      <c r="Y70" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="X68" s="105"/>
-      <c r="Y68" s="105"/>
-      <c r="Z68" s="105"/>
-      <c r="AA68" s="105"/>
-      <c r="AB68" s="105"/>
-      <c r="AC68" s="105"/>
-      <c r="AD68" s="105"/>
-      <c r="AE68" s="105"/>
-      <c r="AF68" s="105"/>
-      <c r="AG68" s="105"/>
-      <c r="AH68" s="105"/>
-      <c r="AI68" s="105"/>
-      <c r="AJ68" s="105"/>
-      <c r="AK68" s="105"/>
-      <c r="AL68" s="105"/>
-      <c r="AM68" s="105"/>
-      <c r="AN68" s="105"/>
-      <c r="AO68" s="108"/>
-    </row>
-    <row r="69" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="89"/>
-      <c r="B69" s="90"/>
-      <c r="C69" s="90"/>
-      <c r="D69" s="90"/>
-      <c r="E69" s="90"/>
-      <c r="F69" s="90"/>
-      <c r="G69" s="90"/>
-      <c r="H69" s="90"/>
-      <c r="I69" s="90"/>
-      <c r="J69" s="91"/>
-      <c r="K69" s="43"/>
-      <c r="L69" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="43"/>
-      <c r="P69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="43"/>
-      <c r="T69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
-      <c r="W69" s="92"/>
-      <c r="X69" s="92"/>
-      <c r="Y69" s="92"/>
-      <c r="Z69" s="92"/>
-      <c r="AA69" s="92"/>
-      <c r="AB69" s="92"/>
-      <c r="AC69" s="92"/>
-      <c r="AD69" s="92"/>
-      <c r="AE69" s="92"/>
-      <c r="AF69" s="92"/>
-      <c r="AG69" s="92"/>
-      <c r="AH69" s="92"/>
-      <c r="AI69" s="92"/>
-      <c r="AJ69" s="92"/>
-      <c r="AK69" s="92"/>
-      <c r="AL69" s="92"/>
-      <c r="AM69" s="92"/>
-      <c r="AN69" s="92"/>
-      <c r="AO69" s="93"/>
-    </row>
-    <row r="70" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="89"/>
-      <c r="B70" s="90"/>
-      <c r="C70" s="90"/>
-      <c r="D70" s="90"/>
-      <c r="E70" s="90"/>
-      <c r="F70" s="90"/>
-      <c r="G70" s="90"/>
-      <c r="H70" s="90"/>
-      <c r="I70" s="90"/>
-      <c r="J70" s="91"/>
-      <c r="K70" s="43"/>
-      <c r="L70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="43"/>
-      <c r="P70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="43"/>
-      <c r="T70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
-      <c r="W70" s="92"/>
-      <c r="X70" s="92"/>
-      <c r="Y70" s="92"/>
-      <c r="Z70" s="92"/>
-      <c r="AA70" s="92"/>
-      <c r="AB70" s="92"/>
-      <c r="AC70" s="92"/>
-      <c r="AD70" s="92"/>
-      <c r="AE70" s="92"/>
-      <c r="AF70" s="92"/>
-      <c r="AG70" s="92"/>
-      <c r="AH70" s="92"/>
-      <c r="AI70" s="92"/>
-      <c r="AJ70" s="92"/>
-      <c r="AK70" s="92"/>
-      <c r="AL70" s="92"/>
-      <c r="AM70" s="92"/>
-      <c r="AN70" s="92"/>
-      <c r="AO70" s="93"/>
-    </row>
-    <row r="71" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="89"/>
-      <c r="B71" s="90"/>
-      <c r="C71" s="90"/>
+      <c r="Z70" s="105"/>
+      <c r="AA70" s="105"/>
+      <c r="AB70" s="105"/>
+      <c r="AC70" s="105"/>
+      <c r="AD70" s="105"/>
+      <c r="AE70" s="105"/>
+      <c r="AF70" s="105"/>
+      <c r="AG70" s="105"/>
+      <c r="AH70" s="105"/>
+      <c r="AI70" s="105"/>
+      <c r="AJ70" s="105"/>
+      <c r="AK70" s="105"/>
+      <c r="AL70" s="105"/>
+      <c r="AM70" s="105"/>
+      <c r="AN70" s="105"/>
+      <c r="AO70" s="105"/>
+      <c r="AP70" s="105"/>
+      <c r="AQ70" s="108"/>
+    </row>
+    <row r="71" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C71" s="89"/>
       <c r="D71" s="90"/>
       <c r="E71" s="90"/>
       <c r="F71" s="90"/>
       <c r="G71" s="90"/>
       <c r="H71" s="90"/>
       <c r="I71" s="90"/>
-      <c r="J71" s="91"/>
-      <c r="K71" s="43"/>
-      <c r="L71" s="1" t="s">
+      <c r="J71" s="90"/>
+      <c r="K71" s="90"/>
+      <c r="L71" s="91"/>
+      <c r="M71" s="43"/>
+      <c r="N71" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="43"/>
-      <c r="P71" s="1" t="s">
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="43"/>
+      <c r="R71" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-      <c r="S71" s="43"/>
-      <c r="T71" s="1" t="s">
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="43"/>
+      <c r="V71" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
-      <c r="W71" s="92"/>
-      <c r="X71" s="92"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
       <c r="Y71" s="92"/>
       <c r="Z71" s="92"/>
       <c r="AA71" s="92"/>
@@ -5682,39 +5581,39 @@
       <c r="AL71" s="92"/>
       <c r="AM71" s="92"/>
       <c r="AN71" s="92"/>
-      <c r="AO71" s="93"/>
-    </row>
-    <row r="72" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="89"/>
-      <c r="B72" s="90"/>
-      <c r="C72" s="90"/>
+      <c r="AO71" s="92"/>
+      <c r="AP71" s="92"/>
+      <c r="AQ71" s="93"/>
+    </row>
+    <row r="72" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C72" s="89"/>
       <c r="D72" s="90"/>
       <c r="E72" s="90"/>
       <c r="F72" s="90"/>
       <c r="G72" s="90"/>
       <c r="H72" s="90"/>
       <c r="I72" s="90"/>
-      <c r="J72" s="91"/>
-      <c r="K72" s="43"/>
-      <c r="L72" s="1" t="s">
+      <c r="J72" s="90"/>
+      <c r="K72" s="90"/>
+      <c r="L72" s="91"/>
+      <c r="M72" s="43"/>
+      <c r="N72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="43"/>
-      <c r="P72" s="1" t="s">
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="43"/>
+      <c r="R72" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="43"/>
-      <c r="T72" s="1" t="s">
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="43"/>
+      <c r="V72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
-      <c r="W72" s="92"/>
-      <c r="X72" s="92"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
       <c r="Y72" s="92"/>
       <c r="Z72" s="92"/>
       <c r="AA72" s="92"/>
@@ -5731,410 +5630,511 @@
       <c r="AL72" s="92"/>
       <c r="AM72" s="92"/>
       <c r="AN72" s="92"/>
-      <c r="AO72" s="93"/>
-    </row>
-    <row r="73" spans="1:41" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="94"/>
-      <c r="B73" s="95"/>
-      <c r="C73" s="95"/>
-      <c r="D73" s="95"/>
-      <c r="E73" s="95"/>
-      <c r="F73" s="95"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
-      <c r="I73" s="95"/>
-      <c r="J73" s="96"/>
-      <c r="K73" s="45"/>
-      <c r="L73" s="34" t="s">
+      <c r="AO72" s="92"/>
+      <c r="AP72" s="92"/>
+      <c r="AQ72" s="93"/>
+    </row>
+    <row r="73" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C73" s="89"/>
+      <c r="D73" s="90"/>
+      <c r="E73" s="90"/>
+      <c r="F73" s="90"/>
+      <c r="G73" s="90"/>
+      <c r="H73" s="90"/>
+      <c r="I73" s="90"/>
+      <c r="J73" s="90"/>
+      <c r="K73" s="90"/>
+      <c r="L73" s="91"/>
+      <c r="M73" s="43"/>
+      <c r="N73" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="34"/>
-      <c r="N73" s="34"/>
-      <c r="O73" s="45"/>
-      <c r="P73" s="34" t="s">
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="43"/>
+      <c r="R73" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q73" s="34"/>
-      <c r="R73" s="34"/>
-      <c r="S73" s="45"/>
-      <c r="T73" s="34" t="s">
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="43"/>
+      <c r="V73" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U73" s="34"/>
-      <c r="V73" s="34"/>
-      <c r="W73" s="97"/>
-      <c r="X73" s="97"/>
-      <c r="Y73" s="97"/>
-      <c r="Z73" s="97"/>
-      <c r="AA73" s="97"/>
-      <c r="AB73" s="97"/>
-      <c r="AC73" s="97"/>
-      <c r="AD73" s="97"/>
-      <c r="AE73" s="97"/>
-      <c r="AF73" s="97"/>
-      <c r="AG73" s="97"/>
-      <c r="AH73" s="97"/>
-      <c r="AI73" s="97"/>
-      <c r="AJ73" s="97"/>
-      <c r="AK73" s="97"/>
-      <c r="AL73" s="97"/>
-      <c r="AM73" s="97"/>
-      <c r="AN73" s="97"/>
-      <c r="AO73" s="98"/>
-    </row>
-    <row r="74" spans="1:41" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="75" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="99" t="s">
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="92"/>
+      <c r="Z73" s="92"/>
+      <c r="AA73" s="92"/>
+      <c r="AB73" s="92"/>
+      <c r="AC73" s="92"/>
+      <c r="AD73" s="92"/>
+      <c r="AE73" s="92"/>
+      <c r="AF73" s="92"/>
+      <c r="AG73" s="92"/>
+      <c r="AH73" s="92"/>
+      <c r="AI73" s="92"/>
+      <c r="AJ73" s="92"/>
+      <c r="AK73" s="92"/>
+      <c r="AL73" s="92"/>
+      <c r="AM73" s="92"/>
+      <c r="AN73" s="92"/>
+      <c r="AO73" s="92"/>
+      <c r="AP73" s="92"/>
+      <c r="AQ73" s="93"/>
+    </row>
+    <row r="74" spans="3:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C74" s="89"/>
+      <c r="D74" s="90"/>
+      <c r="E74" s="90"/>
+      <c r="F74" s="90"/>
+      <c r="G74" s="90"/>
+      <c r="H74" s="90"/>
+      <c r="I74" s="90"/>
+      <c r="J74" s="90"/>
+      <c r="K74" s="90"/>
+      <c r="L74" s="91"/>
+      <c r="M74" s="43"/>
+      <c r="N74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="43"/>
+      <c r="R74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="U74" s="43"/>
+      <c r="V74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="92"/>
+      <c r="Z74" s="92"/>
+      <c r="AA74" s="92"/>
+      <c r="AB74" s="92"/>
+      <c r="AC74" s="92"/>
+      <c r="AD74" s="92"/>
+      <c r="AE74" s="92"/>
+      <c r="AF74" s="92"/>
+      <c r="AG74" s="92"/>
+      <c r="AH74" s="92"/>
+      <c r="AI74" s="92"/>
+      <c r="AJ74" s="92"/>
+      <c r="AK74" s="92"/>
+      <c r="AL74" s="92"/>
+      <c r="AM74" s="92"/>
+      <c r="AN74" s="92"/>
+      <c r="AO74" s="92"/>
+      <c r="AP74" s="92"/>
+      <c r="AQ74" s="93"/>
+    </row>
+    <row r="75" spans="3:43" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C75" s="94"/>
+      <c r="D75" s="95"/>
+      <c r="E75" s="95"/>
+      <c r="F75" s="95"/>
+      <c r="G75" s="95"/>
+      <c r="H75" s="95"/>
+      <c r="I75" s="95"/>
+      <c r="J75" s="95"/>
+      <c r="K75" s="95"/>
+      <c r="L75" s="96"/>
+      <c r="M75" s="45"/>
+      <c r="N75" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="O75" s="34"/>
+      <c r="P75" s="34"/>
+      <c r="Q75" s="45"/>
+      <c r="R75" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="S75" s="34"/>
+      <c r="T75" s="34"/>
+      <c r="U75" s="45"/>
+      <c r="V75" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="W75" s="34"/>
+      <c r="X75" s="34"/>
+      <c r="Y75" s="97"/>
+      <c r="Z75" s="97"/>
+      <c r="AA75" s="97"/>
+      <c r="AB75" s="97"/>
+      <c r="AC75" s="97"/>
+      <c r="AD75" s="97"/>
+      <c r="AE75" s="97"/>
+      <c r="AF75" s="97"/>
+      <c r="AG75" s="97"/>
+      <c r="AH75" s="97"/>
+      <c r="AI75" s="97"/>
+      <c r="AJ75" s="97"/>
+      <c r="AK75" s="97"/>
+      <c r="AL75" s="97"/>
+      <c r="AM75" s="97"/>
+      <c r="AN75" s="97"/>
+      <c r="AO75" s="97"/>
+      <c r="AP75" s="97"/>
+      <c r="AQ75" s="98"/>
+    </row>
+    <row r="76" spans="3:43" ht="5.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="77" spans="3:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C77" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="B75" s="100"/>
-      <c r="C75" s="100"/>
-      <c r="D75" s="100"/>
-      <c r="E75" s="100"/>
-      <c r="F75" s="100"/>
-      <c r="G75" s="100"/>
-      <c r="H75" s="100"/>
-      <c r="I75" s="100"/>
-      <c r="J75" s="100"/>
-      <c r="K75" s="100"/>
-      <c r="L75" s="101"/>
-      <c r="M75" s="102" t="s">
+      <c r="D77" s="100"/>
+      <c r="E77" s="100"/>
+      <c r="F77" s="100"/>
+      <c r="G77" s="100"/>
+      <c r="H77" s="100"/>
+      <c r="I77" s="100"/>
+      <c r="J77" s="100"/>
+      <c r="K77" s="100"/>
+      <c r="L77" s="100"/>
+      <c r="M77" s="100"/>
+      <c r="N77" s="101"/>
+      <c r="O77" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="N75" s="100"/>
-      <c r="O75" s="100"/>
-      <c r="P75" s="100"/>
-      <c r="Q75" s="100"/>
-      <c r="R75" s="100"/>
-      <c r="S75" s="100"/>
-      <c r="T75" s="100"/>
-      <c r="U75" s="100"/>
-      <c r="V75" s="101"/>
-      <c r="W75" s="102" t="s">
+      <c r="P77" s="100"/>
+      <c r="Q77" s="100"/>
+      <c r="R77" s="100"/>
+      <c r="S77" s="100"/>
+      <c r="T77" s="100"/>
+      <c r="U77" s="100"/>
+      <c r="V77" s="100"/>
+      <c r="W77" s="100"/>
+      <c r="X77" s="101"/>
+      <c r="Y77" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="X75" s="100"/>
-      <c r="Y75" s="100"/>
-      <c r="Z75" s="100"/>
-      <c r="AA75" s="100"/>
-      <c r="AB75" s="100"/>
-      <c r="AC75" s="100"/>
-      <c r="AD75" s="100"/>
-      <c r="AE75" s="100"/>
-      <c r="AF75" s="100"/>
-      <c r="AG75" s="100"/>
-      <c r="AH75" s="100"/>
-      <c r="AI75" s="101"/>
-      <c r="AJ75" s="102" t="s">
+      <c r="Z77" s="100"/>
+      <c r="AA77" s="100"/>
+      <c r="AB77" s="100"/>
+      <c r="AC77" s="100"/>
+      <c r="AD77" s="100"/>
+      <c r="AE77" s="100"/>
+      <c r="AF77" s="100"/>
+      <c r="AG77" s="100"/>
+      <c r="AH77" s="100"/>
+      <c r="AI77" s="100"/>
+      <c r="AJ77" s="100"/>
+      <c r="AK77" s="101"/>
+      <c r="AL77" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="AK75" s="100"/>
-      <c r="AL75" s="100"/>
-      <c r="AM75" s="100"/>
-      <c r="AN75" s="100"/>
-      <c r="AO75" s="103"/>
-    </row>
-    <row r="76" spans="1:41" ht="24.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="82" t="s">
+      <c r="AM77" s="100"/>
+      <c r="AN77" s="100"/>
+      <c r="AO77" s="100"/>
+      <c r="AP77" s="100"/>
+      <c r="AQ77" s="103"/>
+    </row>
+    <row r="78" spans="3:43" ht="24.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C78" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="B76" s="83"/>
-      <c r="C76" s="83"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
-      <c r="G76" s="83"/>
-      <c r="H76" s="83"/>
-      <c r="I76" s="83"/>
-      <c r="J76" s="83"/>
-      <c r="K76" s="83"/>
-      <c r="L76" s="84"/>
-      <c r="M76" s="85" t="s">
+      <c r="D78" s="83"/>
+      <c r="E78" s="83"/>
+      <c r="F78" s="83"/>
+      <c r="G78" s="83"/>
+      <c r="H78" s="83"/>
+      <c r="I78" s="83"/>
+      <c r="J78" s="83"/>
+      <c r="K78" s="83"/>
+      <c r="L78" s="83"/>
+      <c r="M78" s="83"/>
+      <c r="N78" s="84"/>
+      <c r="O78" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="N76" s="83"/>
-      <c r="O76" s="83"/>
-      <c r="P76" s="83"/>
-      <c r="Q76" s="83"/>
-      <c r="R76" s="83"/>
-      <c r="S76" s="83"/>
-      <c r="T76" s="83"/>
-      <c r="U76" s="83"/>
-      <c r="V76" s="84"/>
-      <c r="W76" s="85"/>
-      <c r="X76" s="83"/>
-      <c r="Y76" s="83"/>
-      <c r="Z76" s="83"/>
-      <c r="AA76" s="83"/>
-      <c r="AB76" s="83"/>
-      <c r="AC76" s="83"/>
-      <c r="AD76" s="83"/>
-      <c r="AE76" s="83"/>
-      <c r="AF76" s="83"/>
-      <c r="AG76" s="83"/>
-      <c r="AH76" s="83"/>
-      <c r="AI76" s="84"/>
-      <c r="AJ76" s="86" t="s">
+      <c r="P78" s="83"/>
+      <c r="Q78" s="83"/>
+      <c r="R78" s="83"/>
+      <c r="S78" s="83"/>
+      <c r="T78" s="83"/>
+      <c r="U78" s="83"/>
+      <c r="V78" s="83"/>
+      <c r="W78" s="83"/>
+      <c r="X78" s="84"/>
+      <c r="Y78" s="85"/>
+      <c r="Z78" s="83"/>
+      <c r="AA78" s="83"/>
+      <c r="AB78" s="83"/>
+      <c r="AC78" s="83"/>
+      <c r="AD78" s="83"/>
+      <c r="AE78" s="83"/>
+      <c r="AF78" s="83"/>
+      <c r="AG78" s="83"/>
+      <c r="AH78" s="83"/>
+      <c r="AI78" s="83"/>
+      <c r="AJ78" s="83"/>
+      <c r="AK78" s="84"/>
+      <c r="AL78" s="86" t="s">
         <v>198</v>
       </c>
-      <c r="AK76" s="87"/>
-      <c r="AL76" s="87"/>
-      <c r="AM76" s="87"/>
-      <c r="AN76" s="87"/>
-      <c r="AO76" s="88"/>
-    </row>
+      <c r="AM78" s="87"/>
+      <c r="AN78" s="87"/>
+      <c r="AO78" s="87"/>
+      <c r="AP78" s="87"/>
+      <c r="AQ78" s="88"/>
+    </row>
+    <row r="79" spans="3:43" ht="9" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <sheetProtection autoFilter="0"/>
   <protectedRanges>
-    <protectedRange sqref="F11:AO11 AL6 A22:R26 AF63:AF66 AK63:AK66 AK58:AK60 AF58:AF60 AD35 AH35 AL35 AF31 AK31 AF22 AK22 AF15 AK15 O2" name="Intervalo2"/>
-    <protectedRange sqref="AF2" name="Intervalo1_1"/>
+    <protectedRange sqref="H13:AQ13 AN8 C24:T28 AH65:AH68 AM65:AM68 AM60:AM62 AH60:AH62 AF37 AJ37 AN37 AH33 AM33 AH24 AM24 AH17 AM17 Q4" name="Intervalo2"/>
+    <protectedRange sqref="AH4" name="Intervalo1_1"/>
   </protectedRanges>
   <mergeCells count="245">
-    <mergeCell ref="AQ45:AS45"/>
-    <mergeCell ref="AT45:AV45"/>
-    <mergeCell ref="AW45:AY45"/>
-    <mergeCell ref="AZ45:BB45"/>
-    <mergeCell ref="BC45:BE45"/>
-    <mergeCell ref="BF45:BH45"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="O3:AO3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:AB5"/>
-    <mergeCell ref="AC5:AO5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:AB6"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="AF6:AH6"/>
-    <mergeCell ref="AI6:AK6"/>
-    <mergeCell ref="A1:J3"/>
-    <mergeCell ref="K1:AB1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="O2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AO2"/>
-    <mergeCell ref="AL6:AO6"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AA8:AC8"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AO8"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="AA9:AC9"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="AA10:AC10"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AM10:AO10"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="A14:AC14"/>
-    <mergeCell ref="AD14:AO14"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="I18:AC18"/>
-    <mergeCell ref="AD18:AO18"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AA11:AC11"/>
-    <mergeCell ref="AD11:AF11"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="A19:AC19"/>
-    <mergeCell ref="A21:AC21"/>
-    <mergeCell ref="AD21:AO21"/>
-    <mergeCell ref="AD16:AO16"/>
-    <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="AH17:AI17"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="AL17:AM17"/>
-    <mergeCell ref="AN17:AO17"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="A25:W25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AF25:AG25"/>
-    <mergeCell ref="AH25:AI25"/>
-    <mergeCell ref="AJ25:AK25"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AN25:AO25"/>
-    <mergeCell ref="F22:W22"/>
-    <mergeCell ref="X22:AC26"/>
-    <mergeCell ref="A23:W23"/>
-    <mergeCell ref="AD23:AO23"/>
-    <mergeCell ref="A24:W24"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="AH24:AI24"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="A26:W26"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="I27:AC27"/>
-    <mergeCell ref="AD27:AO27"/>
-    <mergeCell ref="A28:AC28"/>
-    <mergeCell ref="A30:AC30"/>
-    <mergeCell ref="AD30:AO30"/>
-    <mergeCell ref="A35:AC35"/>
-    <mergeCell ref="AD32:AO32"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AF33:AG33"/>
-    <mergeCell ref="AH33:AI33"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AL33:AM33"/>
-    <mergeCell ref="AN33:AO33"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="U37:Z37"/>
-    <mergeCell ref="AA37:AO37"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="I34:AC34"/>
-    <mergeCell ref="AD34:AO34"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="L40:T40"/>
-    <mergeCell ref="U40:AE40"/>
-    <mergeCell ref="AF40:AO40"/>
-    <mergeCell ref="B42:AN42"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="L38:T38"/>
-    <mergeCell ref="U38:AE38"/>
-    <mergeCell ref="AF38:AO38"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="L39:T39"/>
-    <mergeCell ref="U39:AE39"/>
-    <mergeCell ref="AF39:AO39"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="AL43:AN43"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="W43:Y43"/>
-    <mergeCell ref="AL44:AN44"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="AC43:AE43"/>
-    <mergeCell ref="AF43:AH43"/>
-    <mergeCell ref="AI43:AK43"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="AF44:AH44"/>
-    <mergeCell ref="AI44:AK44"/>
-    <mergeCell ref="T45:V45"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="AC45:AE45"/>
-    <mergeCell ref="AF45:AH45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="T46:V46"/>
-    <mergeCell ref="W46:Y46"/>
-    <mergeCell ref="AL45:AN45"/>
-    <mergeCell ref="AI45:AK45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="AF46:AH46"/>
-    <mergeCell ref="AI46:AK46"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="A49:U49"/>
-    <mergeCell ref="V49:Y49"/>
-    <mergeCell ref="Z49:AC49"/>
-    <mergeCell ref="AD49:AO49"/>
-    <mergeCell ref="A47:V47"/>
-    <mergeCell ref="W47:AA47"/>
-    <mergeCell ref="A50:U50"/>
-    <mergeCell ref="V50:Y50"/>
-    <mergeCell ref="Z50:AC50"/>
-    <mergeCell ref="B51:L51"/>
-    <mergeCell ref="A55:Y55"/>
-    <mergeCell ref="Z55:AO55"/>
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="M57:T57"/>
-    <mergeCell ref="X57:AC57"/>
-    <mergeCell ref="AD57:AO57"/>
-    <mergeCell ref="A53:U53"/>
-    <mergeCell ref="V53:Y53"/>
-    <mergeCell ref="Z53:AC53"/>
-    <mergeCell ref="A62:AC62"/>
-    <mergeCell ref="AD62:AO62"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="M76:V76"/>
-    <mergeCell ref="W76:AI76"/>
-    <mergeCell ref="AJ76:AO76"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="W72:AO72"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="W73:AO73"/>
-    <mergeCell ref="A75:L75"/>
-    <mergeCell ref="M75:V75"/>
-    <mergeCell ref="W75:AI75"/>
-    <mergeCell ref="AJ75:AO75"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="K68:V68"/>
-    <mergeCell ref="W68:AO68"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="W69:AO69"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="W70:AO70"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="W71:AO71"/>
+    <mergeCell ref="AS47:AU47"/>
+    <mergeCell ref="AV47:AX47"/>
+    <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="BE47:BG47"/>
+    <mergeCell ref="BH47:BJ47"/>
+    <mergeCell ref="BK47:BM47"/>
+    <mergeCell ref="BN47:BP47"/>
+    <mergeCell ref="BQ47:BS47"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="Q5:AQ5"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="J7:AD7"/>
+    <mergeCell ref="AE7:AQ7"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="J8:AD8"/>
+    <mergeCell ref="AE8:AG8"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="C3:L5"/>
+    <mergeCell ref="M3:AD3"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="Q4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="AH4:AQ4"/>
+    <mergeCell ref="AN8:AQ8"/>
+    <mergeCell ref="AL3:AQ3"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AF10:AH10"/>
+    <mergeCell ref="AI10:AK10"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AO10:AQ10"/>
+    <mergeCell ref="W11:Y11"/>
+    <mergeCell ref="Z11:AB11"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="W10:Y10"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AC11:AE11"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="AO11:AQ11"/>
+    <mergeCell ref="AC12:AE12"/>
+    <mergeCell ref="AF12:AH12"/>
+    <mergeCell ref="AI12:AK12"/>
+    <mergeCell ref="AL12:AN12"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AI11:AK11"/>
+    <mergeCell ref="AL11:AN11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="W12:Y12"/>
+    <mergeCell ref="Z12:AB12"/>
+    <mergeCell ref="AF11:AH11"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="C16:AE16"/>
+    <mergeCell ref="AF16:AQ16"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="K20:AE20"/>
+    <mergeCell ref="AF20:AQ20"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="AO13:AQ13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="AF13:AH13"/>
+    <mergeCell ref="AI13:AK13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="Z13:AB13"/>
+    <mergeCell ref="C21:AE21"/>
+    <mergeCell ref="C23:AE23"/>
+    <mergeCell ref="AF23:AQ23"/>
+    <mergeCell ref="AF18:AQ18"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="AH19:AI19"/>
+    <mergeCell ref="AJ19:AK19"/>
+    <mergeCell ref="AL19:AM19"/>
+    <mergeCell ref="AN19:AO19"/>
+    <mergeCell ref="AP19:AQ19"/>
+    <mergeCell ref="AP26:AQ26"/>
+    <mergeCell ref="C27:Y27"/>
+    <mergeCell ref="AF27:AG27"/>
+    <mergeCell ref="AH27:AI27"/>
+    <mergeCell ref="AJ27:AK27"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AN27:AO27"/>
+    <mergeCell ref="AP27:AQ27"/>
+    <mergeCell ref="H24:Y24"/>
+    <mergeCell ref="Z24:AE28"/>
+    <mergeCell ref="C25:Y25"/>
+    <mergeCell ref="AF25:AQ25"/>
+    <mergeCell ref="C26:Y26"/>
+    <mergeCell ref="AF26:AG26"/>
+    <mergeCell ref="AH26:AI26"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AN26:AO26"/>
+    <mergeCell ref="C28:Y28"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="K29:AE29"/>
+    <mergeCell ref="AF29:AQ29"/>
+    <mergeCell ref="C30:AE30"/>
+    <mergeCell ref="C32:AE32"/>
+    <mergeCell ref="AF32:AQ32"/>
+    <mergeCell ref="C37:AE37"/>
+    <mergeCell ref="AF34:AQ34"/>
+    <mergeCell ref="AF35:AG35"/>
+    <mergeCell ref="AH35:AI35"/>
+    <mergeCell ref="AJ35:AK35"/>
+    <mergeCell ref="AL35:AM35"/>
+    <mergeCell ref="AN35:AO35"/>
+    <mergeCell ref="AP35:AQ35"/>
+    <mergeCell ref="C39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="W39:AB39"/>
+    <mergeCell ref="AC39:AQ39"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="K36:AE36"/>
+    <mergeCell ref="AF36:AQ36"/>
+    <mergeCell ref="C42:M42"/>
+    <mergeCell ref="N42:V42"/>
+    <mergeCell ref="W42:AG42"/>
+    <mergeCell ref="AH42:AQ42"/>
+    <mergeCell ref="D44:AP44"/>
+    <mergeCell ref="C40:M40"/>
+    <mergeCell ref="N40:V40"/>
+    <mergeCell ref="W40:AG40"/>
+    <mergeCell ref="AH40:AQ40"/>
+    <mergeCell ref="C41:M41"/>
+    <mergeCell ref="N41:V41"/>
+    <mergeCell ref="W41:AG41"/>
+    <mergeCell ref="AH41:AQ41"/>
+    <mergeCell ref="AN45:AP45"/>
+    <mergeCell ref="V45:X45"/>
+    <mergeCell ref="Y45:AA45"/>
+    <mergeCell ref="AN46:AP46"/>
+    <mergeCell ref="AB45:AD45"/>
+    <mergeCell ref="AE45:AG45"/>
+    <mergeCell ref="AH45:AJ45"/>
+    <mergeCell ref="AK45:AM45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="P45:R45"/>
+    <mergeCell ref="S45:U45"/>
+    <mergeCell ref="AB46:AD46"/>
+    <mergeCell ref="AE46:AG46"/>
+    <mergeCell ref="AH46:AJ46"/>
+    <mergeCell ref="AK46:AM46"/>
+    <mergeCell ref="V47:X47"/>
+    <mergeCell ref="Y47:AA47"/>
+    <mergeCell ref="AB47:AD47"/>
+    <mergeCell ref="AE47:AG47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="P48:R48"/>
+    <mergeCell ref="S48:U48"/>
+    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="Y48:AA48"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="P46:R46"/>
+    <mergeCell ref="S46:U46"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="Y46:AA46"/>
+    <mergeCell ref="AN47:AP47"/>
+    <mergeCell ref="AK47:AM47"/>
+    <mergeCell ref="AB48:AD48"/>
+    <mergeCell ref="AE48:AG48"/>
+    <mergeCell ref="AH48:AJ48"/>
+    <mergeCell ref="AK48:AM48"/>
+    <mergeCell ref="AN48:AP48"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="P47:R47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="C51:W51"/>
+    <mergeCell ref="X51:AA51"/>
+    <mergeCell ref="AB51:AE51"/>
+    <mergeCell ref="AF51:AQ51"/>
+    <mergeCell ref="C49:X49"/>
+    <mergeCell ref="Y49:AC49"/>
+    <mergeCell ref="C52:W52"/>
+    <mergeCell ref="X52:AA52"/>
+    <mergeCell ref="AB52:AE52"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="C57:AA57"/>
+    <mergeCell ref="AB57:AQ57"/>
+    <mergeCell ref="C59:N59"/>
+    <mergeCell ref="O59:V59"/>
+    <mergeCell ref="Z59:AE59"/>
+    <mergeCell ref="AF59:AQ59"/>
+    <mergeCell ref="C55:W55"/>
+    <mergeCell ref="X55:AA55"/>
+    <mergeCell ref="AB55:AE55"/>
+    <mergeCell ref="C64:AE64"/>
+    <mergeCell ref="AF64:AQ64"/>
+    <mergeCell ref="C78:N78"/>
+    <mergeCell ref="O78:X78"/>
+    <mergeCell ref="Y78:AK78"/>
+    <mergeCell ref="AL78:AQ78"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="Y74:AQ74"/>
+    <mergeCell ref="C75:L75"/>
+    <mergeCell ref="Y75:AQ75"/>
+    <mergeCell ref="C77:N77"/>
+    <mergeCell ref="O77:X77"/>
+    <mergeCell ref="Y77:AK77"/>
+    <mergeCell ref="AL77:AQ77"/>
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="M70:X70"/>
+    <mergeCell ref="Y70:AQ70"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="Y71:AQ71"/>
+    <mergeCell ref="C72:L72"/>
+    <mergeCell ref="Y72:AQ72"/>
+    <mergeCell ref="C73:L73"/>
+    <mergeCell ref="Y73:AQ73"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
